--- a/GSYH_Oncu.xlsx
+++ b/GSYH_Oncu.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/omerozogul/Desktop/DashboardProje/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\splktfs\Aktif Pasif Yonetimi\Aktif Pasif\PARA PİYASALARI\Reports\APKO\APKO Veriler\github_excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A0B68F3-45D7-3844-9F62-C9B26BE454B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E73936-E290-4870-98E2-8815962BF1C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14520" yWindow="0" windowWidth="14280" windowHeight="18000" xr2:uid="{1B6B32CB-0B38-2A40-A469-C0726E1D7DB3}"/>
+    <workbookView xWindow="28710" yWindow="-16440" windowWidth="29040" windowHeight="15720" xr2:uid="{1B6B32CB-0B38-2A40-A469-C0726E1D7DB3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,34 +35,49 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
   <si>
     <t>Tarih</t>
-  </si>
-  <si>
-    <t>Hizmet</t>
-  </si>
-  <si>
-    <t>Ticaret</t>
-  </si>
-  <si>
-    <t>Perakende</t>
-  </si>
-  <si>
-    <t>İnşaat</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Sanayi</t>
+    <t>Hizmet takvim ar.</t>
+  </si>
+  <si>
+    <t>Hizmet mevsim ar.</t>
+  </si>
+  <si>
+    <t>Sanayi takvim ar.</t>
+  </si>
+  <si>
+    <t>Sanayi mevsim ar.</t>
+  </si>
+  <si>
+    <t>Perakende takvim ar.</t>
+  </si>
+  <si>
+    <t>Perakende mevsim ar.</t>
+  </si>
+  <si>
+    <t>İnşaat takvim ar.</t>
+  </si>
+  <si>
+    <t>İnşaat mevsim ar.</t>
+  </si>
+  <si>
+    <t>Ticaret mevsim ar.</t>
+  </si>
+  <si>
+    <t>Ticaret takvim ar.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -129,9 +144,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -169,7 +184,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -275,7 +290,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -417,7 +432,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -425,2181 +440,3850 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4ED4A95-7921-FD4E-9C87-384BD929F506}">
-  <dimension ref="A1:I112"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <dimension ref="A1:O112"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.09765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="19.19921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.19921875" customWidth="1"/>
+    <col min="8" max="8" width="15.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.3984375" customWidth="1"/>
+    <col min="10" max="11" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="1.3984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="G1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>42736</v>
       </c>
       <c r="B2" s="2">
+        <v>64.773115807370388</v>
+      </c>
+      <c r="C2" s="2">
         <v>79.238805873588603</v>
       </c>
-      <c r="C2" s="2">
+      <c r="D2" s="2">
+        <v>66.375778776611696</v>
+      </c>
+      <c r="E2" s="2">
         <v>80.05598689354899</v>
       </c>
-      <c r="D2" s="2">
+      <c r="F2" s="2">
+        <v>67.590513786142708</v>
+      </c>
+      <c r="G2" s="2">
         <v>80.0336005266809</v>
       </c>
-      <c r="E2" s="2">
+      <c r="H2" s="2">
+        <v>96.337778223564598</v>
+      </c>
+      <c r="I2" s="2">
         <v>96.933550715604298</v>
       </c>
-      <c r="F2" s="2">
+      <c r="J2" s="2">
         <v>70.010800261924899</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="K2" s="2">
+        <v>77.820123028575964</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>42767</v>
       </c>
       <c r="B3" s="2">
+        <v>67.979570131639292</v>
+      </c>
+      <c r="C3" s="2">
         <v>81.227622410360894</v>
       </c>
-      <c r="C3" s="2">
+      <c r="D3" s="2">
+        <v>70.028952320282499</v>
+      </c>
+      <c r="E3" s="2">
         <v>82.587456705824607</v>
       </c>
-      <c r="D3" s="2">
+      <c r="F3" s="2">
+        <v>67.562108106675495</v>
+      </c>
+      <c r="G3" s="2">
         <v>81.073383058604989</v>
       </c>
-      <c r="E3" s="2">
+      <c r="H3" s="2">
+        <v>91.044894212935006</v>
+      </c>
+      <c r="I3" s="2">
         <v>100.568933218613</v>
       </c>
-      <c r="F3" s="2">
+      <c r="J3" s="2">
         <v>70.327274838591038</v>
       </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="K3" s="2">
+        <v>79.053752261011994</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>42795</v>
       </c>
       <c r="B4" s="2">
+        <v>77.101949108306201</v>
+      </c>
+      <c r="C4" s="2">
         <v>80.997381548995691</v>
       </c>
-      <c r="C4" s="2">
+      <c r="D4" s="2">
+        <v>82.167155182508282</v>
+      </c>
+      <c r="E4" s="2">
         <v>82.761769223989504</v>
       </c>
-      <c r="D4" s="2">
+      <c r="F4" s="2">
+        <v>78.277836302085788</v>
+      </c>
+      <c r="G4" s="2">
         <v>81.631102209392608</v>
       </c>
-      <c r="E4" s="2">
+      <c r="H4" s="2">
+        <v>88.889995885266501</v>
+      </c>
+      <c r="I4" s="2">
         <v>107.123623990474</v>
       </c>
-      <c r="F4" s="2">
+      <c r="J4" s="2">
         <v>80.735740615830053</v>
       </c>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="K4" s="2">
+        <v>80.097799498718985</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>42826</v>
       </c>
       <c r="B5" s="2">
+        <v>76.700569057947604</v>
+      </c>
+      <c r="C5" s="2">
         <v>82.0635249139563</v>
       </c>
-      <c r="C5" s="2">
+      <c r="D5" s="2">
+        <v>79.054273438028687</v>
+      </c>
+      <c r="E5" s="2">
         <v>82.228495442749107</v>
       </c>
-      <c r="D5" s="2">
+      <c r="F5" s="2">
+        <v>77.370854973246594</v>
+      </c>
+      <c r="G5" s="2">
         <v>81.779737254012502</v>
       </c>
-      <c r="E5" s="2">
+      <c r="H5" s="2">
+        <v>102.00365004702699</v>
+      </c>
+      <c r="I5" s="2">
         <v>112.864174782932</v>
       </c>
-      <c r="F5" s="2">
+      <c r="J5" s="2">
         <v>80.530586139592856</v>
       </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="K5" s="2">
+        <v>82.290896018752051</v>
+      </c>
+      <c r="O5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>42856</v>
       </c>
       <c r="B6" s="2">
+        <v>80.79088414518489</v>
+      </c>
+      <c r="C6" s="2">
         <v>83.406529538536191</v>
       </c>
-      <c r="C6" s="2">
+      <c r="D6" s="2">
+        <v>86.421834537753881</v>
+      </c>
+      <c r="E6" s="2">
         <v>85.854758593713683</v>
       </c>
-      <c r="D6" s="2">
+      <c r="F6" s="2">
+        <v>82.697217652472503</v>
+      </c>
+      <c r="G6" s="2">
         <v>82.953478258972083</v>
       </c>
-      <c r="E6" s="2">
+      <c r="H6" s="2">
+        <v>115.904235461216</v>
+      </c>
+      <c r="I6" s="2">
         <v>118.584349568172</v>
       </c>
-      <c r="F6" s="2">
+      <c r="J6" s="2">
         <v>81.76394293496098</v>
       </c>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="K6" s="2">
+        <v>81.264642650821884</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>42887</v>
       </c>
       <c r="B7" s="2">
+        <v>83.023434408809592</v>
+      </c>
+      <c r="C7" s="2">
         <v>82.605150941868885</v>
       </c>
-      <c r="C7" s="2">
+      <c r="D7" s="2">
+        <v>87.576279756143506</v>
+      </c>
+      <c r="E7" s="2">
         <v>85.144022924091004</v>
       </c>
-      <c r="D7" s="2">
+      <c r="F7" s="2">
+        <v>85.289145037354686</v>
+      </c>
+      <c r="G7" s="2">
         <v>82.498692525436496</v>
       </c>
-      <c r="E7" s="2">
+      <c r="H7" s="2">
+        <v>121.89192970253301</v>
+      </c>
+      <c r="I7" s="2">
         <v>122.316435936419</v>
       </c>
-      <c r="F7" s="2">
+      <c r="J7" s="2">
         <v>82.561535775111281</v>
       </c>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="K7" s="2">
+        <v>81.726213532929876</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>42917</v>
       </c>
       <c r="B8" s="2">
+        <v>84.987961385023098</v>
+      </c>
+      <c r="C8" s="2">
         <v>83.479644334514987</v>
       </c>
-      <c r="C8" s="2">
+      <c r="D8" s="2">
+        <v>89.2979019205317</v>
+      </c>
+      <c r="E8" s="2">
         <v>88.320701661468405</v>
       </c>
-      <c r="D8" s="2">
+      <c r="F8" s="2">
+        <v>87.864136687275305</v>
+      </c>
+      <c r="G8" s="2">
         <v>84.377273129822214</v>
       </c>
-      <c r="E8" s="2">
+      <c r="H8" s="2">
+        <v>123.51458470855501</v>
+      </c>
+      <c r="I8" s="2">
         <v>122.057350874658</v>
       </c>
-      <c r="F8" s="2">
+      <c r="J8" s="2">
         <v>82.999472923380338</v>
       </c>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="K8" s="2">
+        <v>81.561113285399429</v>
+      </c>
+      <c r="L8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>42948</v>
       </c>
       <c r="B9" s="2">
+        <v>86.262051246553298</v>
+      </c>
+      <c r="C9" s="2">
         <v>84.320704461723096</v>
       </c>
-      <c r="C9" s="2">
+      <c r="D9" s="2">
+        <v>87.977876157255096</v>
+      </c>
+      <c r="E9" s="2">
         <v>87.1657375508196</v>
       </c>
-      <c r="D9" s="2">
+      <c r="F9" s="2">
+        <v>90.586450780417607</v>
+      </c>
+      <c r="G9" s="2">
         <v>85.4418112990693</v>
       </c>
-      <c r="E9" s="2">
+      <c r="H9" s="2">
+        <v>127.09372179681</v>
+      </c>
+      <c r="I9" s="2">
         <v>123.915835792462</v>
       </c>
-      <c r="F9" s="2">
+      <c r="J9" s="2">
         <v>82.841756990403297</v>
       </c>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="K9" s="2">
+        <v>84.11631380042364</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>42979</v>
       </c>
       <c r="B10" s="2">
+        <v>90.338375568685393</v>
+      </c>
+      <c r="C10" s="2">
         <v>86.2787186152446</v>
       </c>
-      <c r="C10" s="2">
+      <c r="D10" s="2">
+        <v>92.394316681088597</v>
+      </c>
+      <c r="E10" s="2">
         <v>87.898716515351396</v>
       </c>
-      <c r="D10" s="2">
+      <c r="F10" s="2">
+        <v>89.752671759255492</v>
+      </c>
+      <c r="G10" s="2">
         <v>85.399575320136591</v>
       </c>
-      <c r="E10" s="2">
+      <c r="H10" s="2">
+        <v>134.851450318773</v>
+      </c>
+      <c r="I10" s="2">
         <v>129.51509712251899</v>
       </c>
-      <c r="F10" s="2">
+      <c r="J10" s="2">
         <v>88.679017448314397</v>
       </c>
-      <c r="G10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="K10" s="2">
+        <v>85.157997208176596</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>43009</v>
       </c>
       <c r="B11" s="2">
+        <v>89.823174296711088</v>
+      </c>
+      <c r="C11" s="2">
         <v>87.295436558829394</v>
       </c>
-      <c r="C11" s="2">
+      <c r="D11" s="2">
+        <v>90.299711696202408</v>
+      </c>
+      <c r="E11" s="2">
         <v>86.995812992887494</v>
       </c>
-      <c r="D11" s="2">
+      <c r="F11" s="2">
+        <v>86.730821391381895</v>
+      </c>
+      <c r="G11" s="2">
         <v>85.088634581707396</v>
       </c>
-      <c r="E11" s="2">
+      <c r="H11" s="2">
+        <v>136.20221581763201</v>
+      </c>
+      <c r="I11" s="2">
         <v>128.58923341115499</v>
       </c>
-      <c r="F11" s="2">
+      <c r="J11" s="2">
         <v>90.807704169997933</v>
       </c>
-      <c r="I11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="K11" s="2">
+        <v>85.517066977664896</v>
+      </c>
+      <c r="M11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>43040</v>
       </c>
       <c r="B12" s="2">
+        <v>86.99577222728621</v>
+      </c>
+      <c r="C12" s="2">
         <v>87.543755223823098</v>
       </c>
-      <c r="C12" s="2">
+      <c r="D12" s="2">
+        <v>90.186224464437601</v>
+      </c>
+      <c r="E12" s="2">
         <v>86.917216773140694</v>
       </c>
-      <c r="D12" s="2">
+      <c r="F12" s="2">
+        <v>84.191026609985201</v>
+      </c>
+      <c r="G12" s="2">
         <v>84.846103703805099</v>
       </c>
-      <c r="E12" s="2">
+      <c r="H12" s="2">
+        <v>138.50725217970401</v>
+      </c>
+      <c r="I12" s="2">
         <v>127.69414268683499</v>
       </c>
-      <c r="F12" s="2">
+      <c r="J12" s="2">
         <v>89.668268088969995</v>
       </c>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="K12" s="2">
+        <v>86.047947833110527</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>43070</v>
       </c>
       <c r="B13" s="2">
+        <v>116.17151752398901</v>
+      </c>
+      <c r="C13" s="2">
         <v>89.227580662919181</v>
       </c>
-      <c r="C13" s="2">
+      <c r="D13" s="2">
+        <v>103.42654606608001</v>
+      </c>
+      <c r="E13" s="2">
         <v>87.53384778334069</v>
       </c>
-      <c r="D13" s="2">
+      <c r="F13" s="2">
+        <v>101.26632264193499</v>
+      </c>
+      <c r="G13" s="2">
         <v>86.739030790000896</v>
       </c>
-      <c r="E13" s="2">
+      <c r="H13" s="2">
+        <v>148.84644834314801</v>
+      </c>
+      <c r="I13" s="2">
         <v>129.22342674687499</v>
       </c>
-      <c r="F13" s="2">
+      <c r="J13" s="2">
         <v>96.294867185025382</v>
       </c>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="K13" s="2">
+        <v>88.29286056885573</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>43101</v>
       </c>
       <c r="B14" s="2">
+        <v>74.278697891993289</v>
+      </c>
+      <c r="C14" s="2">
         <v>89.714822999923399</v>
       </c>
-      <c r="C14" s="2">
+      <c r="D14" s="2">
+        <v>72.359377286670693</v>
+      </c>
+      <c r="E14" s="2">
         <v>86.631036862717593</v>
       </c>
-      <c r="D14" s="2">
+      <c r="F14" s="2">
+        <v>73.918081853852513</v>
+      </c>
+      <c r="G14" s="2">
         <v>87.209320338922993</v>
       </c>
-      <c r="E14" s="2">
+      <c r="H14" s="2">
+        <v>136.50501743949701</v>
+      </c>
+      <c r="I14" s="2">
         <v>136.544902933473</v>
       </c>
-      <c r="F14" s="2">
+      <c r="J14" s="2">
         <v>78.168875739311645</v>
       </c>
-    </row>
-    <row r="15" spans="1:9">
+      <c r="K14" s="2">
+        <v>86.609770755627721</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>43132</v>
       </c>
       <c r="B15" s="2">
+        <v>74.783427845554897</v>
+      </c>
+      <c r="C15" s="2">
         <v>89.132073930641681</v>
       </c>
-      <c r="C15" s="2">
+      <c r="D15" s="2">
+        <v>73.428013629810906</v>
+      </c>
+      <c r="E15" s="2">
         <v>86.20950668454789</v>
       </c>
-      <c r="D15" s="2">
+      <c r="F15" s="2">
+        <v>72.228723677816603</v>
+      </c>
+      <c r="G15" s="2">
         <v>86.384540158391601</v>
       </c>
-      <c r="E15" s="2">
+      <c r="H15" s="2">
+        <v>122.55761601768801</v>
+      </c>
+      <c r="I15" s="2">
         <v>132.86814294540699</v>
       </c>
-      <c r="F15" s="2">
+      <c r="J15" s="2">
         <v>76.989500007991666</v>
       </c>
-    </row>
-    <row r="16" spans="1:9">
+      <c r="K15" s="2">
+        <v>86.044379232759738</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>43160</v>
       </c>
       <c r="B16" s="2">
+        <v>84.445467022405495</v>
+      </c>
+      <c r="C16" s="2">
         <v>88.653655331319797</v>
       </c>
-      <c r="C16" s="2">
+      <c r="D16" s="2">
+        <v>86.988093515382388</v>
+      </c>
+      <c r="E16" s="2">
         <v>86.457775450727809</v>
       </c>
-      <c r="D16" s="2">
+      <c r="F16" s="2">
+        <v>83.317575195018691</v>
+      </c>
+      <c r="G16" s="2">
         <v>85.982444547625803</v>
       </c>
-      <c r="E16" s="2">
+      <c r="H16" s="2">
+        <v>107.916530918623</v>
+      </c>
+      <c r="I16" s="2">
         <v>127.573333375877</v>
       </c>
-      <c r="F16" s="2">
+      <c r="J16" s="2">
         <v>86.678549457954574</v>
       </c>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="K16" s="2">
+        <v>86.093047757191911</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>43191</v>
       </c>
       <c r="B17" s="2">
+        <v>83.73679197625529</v>
+      </c>
+      <c r="C17" s="2">
         <v>89.324266863793994</v>
       </c>
-      <c r="C17" s="2">
+      <c r="D17" s="2">
+        <v>86.160631074429887</v>
+      </c>
+      <c r="E17" s="2">
         <v>89.107023499475403</v>
       </c>
-      <c r="D17" s="2">
+      <c r="F17" s="2">
+        <v>82.966546507704493</v>
+      </c>
+      <c r="G17" s="2">
         <v>86.981735129182098</v>
       </c>
-      <c r="E17" s="2">
+      <c r="H17" s="2">
+        <v>115.93466950784</v>
+      </c>
+      <c r="I17" s="2">
         <v>127.83253352075801</v>
       </c>
-      <c r="F17" s="2">
+      <c r="J17" s="2">
         <v>85.269485600674003</v>
       </c>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="K17" s="2">
+        <v>87.155386129421103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>43221</v>
       </c>
       <c r="B18" s="2">
+        <v>84.332339910631987</v>
+      </c>
+      <c r="C18" s="2">
         <v>87.383414613995811</v>
       </c>
-      <c r="C18" s="2">
+      <c r="D18" s="2">
+        <v>85.572678116027504</v>
+      </c>
+      <c r="E18" s="2">
         <v>85.417912769406712</v>
       </c>
-      <c r="D18" s="2">
+      <c r="F18" s="2">
+        <v>85.771362188340092</v>
+      </c>
+      <c r="G18" s="2">
         <v>85.813230033787491</v>
       </c>
-      <c r="E18" s="2">
+      <c r="H18" s="2">
+        <v>124.976223970508</v>
+      </c>
+      <c r="I18" s="2">
         <v>128.38340299878001</v>
       </c>
-      <c r="F18" s="2">
+      <c r="J18" s="2">
         <v>86.567629842758151</v>
       </c>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="K18" s="2">
+        <v>85.864509808454258</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>43252</v>
       </c>
       <c r="B19" s="2">
+        <v>88.122532032374394</v>
+      </c>
+      <c r="C19" s="2">
         <v>86.858979399241989</v>
       </c>
-      <c r="C19" s="2">
+      <c r="D19" s="2">
+        <v>84.833456394194599</v>
+      </c>
+      <c r="E19" s="2">
         <v>82.411645138925692</v>
       </c>
-      <c r="D19" s="2">
+      <c r="F19" s="2">
+        <v>88.789538222731593</v>
+      </c>
+      <c r="G19" s="2">
         <v>85.046166945045499</v>
       </c>
-      <c r="E19" s="2">
+      <c r="H19" s="2">
+        <v>124.67413635114499</v>
+      </c>
+      <c r="I19" s="2">
         <v>125.83168148701</v>
       </c>
-      <c r="F19" s="2">
+      <c r="J19" s="2">
         <v>84.297071959130349</v>
       </c>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="K19" s="2">
+        <v>83.429431820593365</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>43282</v>
       </c>
       <c r="B20" s="2">
+        <v>89.524548166173702</v>
+      </c>
+      <c r="C20" s="2">
         <v>87.170877253276586</v>
       </c>
-      <c r="C20" s="2">
+      <c r="D20" s="2">
+        <v>84.099791044332193</v>
+      </c>
+      <c r="E20" s="2">
         <v>82.970878410376699</v>
       </c>
-      <c r="D20" s="2">
+      <c r="F20" s="2">
+        <v>88.966052381926687</v>
+      </c>
+      <c r="G20" s="2">
         <v>85.057601919000689</v>
       </c>
-      <c r="E20" s="2">
+      <c r="H20" s="2">
+        <v>120.90910807466901</v>
+      </c>
+      <c r="I20" s="2">
         <v>119.897982496981</v>
       </c>
-      <c r="F20" s="2">
+      <c r="J20" s="2">
         <v>87.249699785957404</v>
       </c>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="K20" s="2">
+        <v>85.450269624313307</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>43313</v>
       </c>
       <c r="B21" s="2">
+        <v>90.887401847752699</v>
+      </c>
+      <c r="C21" s="2">
         <v>88.702114403626496</v>
       </c>
-      <c r="C21" s="2">
+      <c r="D21" s="2">
+        <v>85.889790668425803</v>
+      </c>
+      <c r="E21" s="2">
         <v>84.6111447357938</v>
       </c>
-      <c r="D21" s="2">
+      <c r="F21" s="2">
+        <v>91.874190494222901</v>
+      </c>
+      <c r="G21" s="2">
         <v>86.052232203836397</v>
       </c>
-      <c r="E21" s="2">
+      <c r="H21" s="2">
+        <v>116.18803565947501</v>
+      </c>
+      <c r="I21" s="2">
         <v>113.481111802909</v>
       </c>
-      <c r="F21" s="2">
+      <c r="J21" s="2">
         <v>84.508590161169309</v>
       </c>
-    </row>
-    <row r="22" spans="1:6">
+      <c r="K21" s="2">
+        <v>85.190348906457857</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>43344</v>
       </c>
       <c r="B22" s="2">
+        <v>90.781653602373098</v>
+      </c>
+      <c r="C22" s="2">
         <v>86.047794084816687</v>
       </c>
-      <c r="C22" s="2">
+      <c r="D22" s="2">
+        <v>80.85082733886739</v>
+      </c>
+      <c r="E22" s="2">
         <v>76.977873727136199</v>
       </c>
-      <c r="D22" s="2">
+      <c r="F22" s="2">
+        <v>83.877514302630686</v>
+      </c>
+      <c r="G22" s="2">
         <v>81.08956473264</v>
       </c>
-      <c r="E22" s="2">
+      <c r="H22" s="2">
+        <v>109.78861825163899</v>
+      </c>
+      <c r="I22" s="2">
         <v>105.53660234107601</v>
       </c>
-      <c r="F22" s="2">
+      <c r="J22" s="2">
         <v>85.424896280382697</v>
       </c>
-    </row>
-    <row r="23" spans="1:6">
+      <c r="K22" s="2">
+        <v>82.484760444408465</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>43374</v>
       </c>
       <c r="B23" s="2">
+        <v>88.756641924336108</v>
+      </c>
+      <c r="C23" s="2">
         <v>86.309321819982699</v>
       </c>
-      <c r="C23" s="2">
+      <c r="D23" s="2">
+        <v>75.13600757171379</v>
+      </c>
+      <c r="E23" s="2">
         <v>73.054950604366695</v>
       </c>
-      <c r="D23" s="2">
+      <c r="F23" s="2">
+        <v>78.342279495770299</v>
+      </c>
+      <c r="G23" s="2">
         <v>78.322442834381889</v>
       </c>
-      <c r="E23" s="2">
+      <c r="H23" s="2">
+        <v>104.373487160826</v>
+      </c>
+      <c r="I23" s="2">
         <v>97.7099601058096</v>
       </c>
-      <c r="F23" s="2">
+      <c r="J23" s="2">
         <v>85.058580713105783</v>
       </c>
-    </row>
-    <row r="24" spans="1:6">
+      <c r="K23" s="2">
+        <v>80.788222788094373</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>43405</v>
       </c>
       <c r="B24" s="2">
+        <v>83.697857223519094</v>
+      </c>
+      <c r="C24" s="2">
         <v>85.183375735825805</v>
       </c>
-      <c r="C24" s="2">
+      <c r="D24" s="2">
+        <v>76.843170310267894</v>
+      </c>
+      <c r="E24" s="2">
         <v>74.989621427266997</v>
       </c>
-      <c r="D24" s="2">
+      <c r="F24" s="2">
+        <v>77.202195724159196</v>
+      </c>
+      <c r="G24" s="2">
         <v>78.724745166040805</v>
       </c>
-      <c r="E24" s="2">
+      <c r="H24" s="2">
+        <v>105.388222355542</v>
+      </c>
+      <c r="I24" s="2">
         <v>95.261771969877998</v>
       </c>
-      <c r="F24" s="2">
+      <c r="J24" s="2">
         <v>83.326610566071508</v>
       </c>
-    </row>
-    <row r="25" spans="1:6">
+      <c r="K24" s="2">
+        <v>80.647912573462747</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>43435</v>
       </c>
       <c r="B25" s="2">
+        <v>111.25890821481201</v>
+      </c>
+      <c r="C25" s="2">
         <v>85.819573435855887</v>
       </c>
-      <c r="C25" s="2">
+      <c r="D25" s="2">
+        <v>87.561573364581093</v>
+      </c>
+      <c r="E25" s="2">
         <v>75.461903740946084</v>
       </c>
-      <c r="D25" s="2">
+      <c r="F25" s="2">
+        <v>90.664408986923803</v>
+      </c>
+      <c r="G25" s="2">
         <v>79.184550934836807</v>
       </c>
-      <c r="E25" s="2">
+      <c r="H25" s="2">
+        <v>108.207683901455</v>
+      </c>
+      <c r="I25" s="2">
         <v>90.082640744998599</v>
       </c>
-      <c r="F25" s="2">
+      <c r="J25" s="2">
         <v>86.831351847892108</v>
       </c>
-    </row>
-    <row r="26" spans="1:6">
+      <c r="K25" s="2">
+        <v>79.328833209709444</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>43466</v>
       </c>
       <c r="B26" s="2">
+        <v>71.560036555516987</v>
+      </c>
+      <c r="C26" s="2">
         <v>87.540017480240095</v>
       </c>
-      <c r="C26" s="2">
+      <c r="D26" s="2">
+        <v>63.739718919907297</v>
+      </c>
+      <c r="E26" s="2">
         <v>76.073467112450686</v>
       </c>
-      <c r="D26" s="2">
+      <c r="F26" s="2">
+        <v>67.9687703268186</v>
+      </c>
+      <c r="G26" s="2">
         <v>79.990597020504595</v>
       </c>
-      <c r="E26" s="2">
+      <c r="H26" s="2">
+        <v>115.933856901498</v>
+      </c>
+      <c r="I26" s="2">
         <v>115.883793549514</v>
       </c>
-      <c r="F26" s="2">
+      <c r="J26" s="2">
         <v>72.181139586601518</v>
       </c>
-    </row>
-    <row r="27" spans="1:6">
+      <c r="K26" s="2">
+        <v>80.704455191780411</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>43497</v>
       </c>
       <c r="B27" s="2">
+        <v>73.476888115650212</v>
+      </c>
+      <c r="C27" s="2">
         <v>88.465994605122788</v>
       </c>
-      <c r="C27" s="2">
+      <c r="D27" s="2">
+        <v>65.711483959467714</v>
+      </c>
+      <c r="E27" s="2">
         <v>76.971529005925689</v>
       </c>
-      <c r="D27" s="2">
+      <c r="F27" s="2">
+        <v>67.690101434347994</v>
+      </c>
+      <c r="G27" s="2">
         <v>80.525991510792281</v>
       </c>
-      <c r="E27" s="2">
+      <c r="H27" s="2">
+        <v>102.690305789265</v>
+      </c>
+      <c r="I27" s="2">
         <v>112.181146282545</v>
       </c>
-      <c r="F27" s="2">
+      <c r="J27" s="2">
         <v>73.102810800585686</v>
       </c>
-    </row>
-    <row r="28" spans="1:6">
+      <c r="K27" s="2">
+        <v>81.633131291886812</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>43525</v>
       </c>
       <c r="B28" s="2">
+        <v>85.840975544677903</v>
+      </c>
+      <c r="C28" s="2">
         <v>90.343054652752301</v>
       </c>
-      <c r="C28" s="2">
+      <c r="D28" s="2">
+        <v>80.27150208725061</v>
+      </c>
+      <c r="E28" s="2">
         <v>79.763944418877998</v>
       </c>
-      <c r="D28" s="2">
+      <c r="F28" s="2">
+        <v>79.418310234177994</v>
+      </c>
+      <c r="G28" s="2">
         <v>81.946553174578796</v>
       </c>
-      <c r="E28" s="2">
+      <c r="H28" s="2">
+        <v>91.012080288314806</v>
+      </c>
+      <c r="I28" s="2">
         <v>109.851447496943</v>
       </c>
-      <c r="F28" s="2">
+      <c r="J28" s="2">
         <v>85.152924307918994</v>
       </c>
-    </row>
-    <row r="29" spans="1:6">
+      <c r="K28" s="2">
+        <v>84.080545848183647</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>43556</v>
       </c>
       <c r="B29" s="2">
+        <v>82.907239134147801</v>
+      </c>
+      <c r="C29" s="2">
         <v>89.163620361023092</v>
       </c>
-      <c r="C29" s="2">
+      <c r="D29" s="2">
+        <v>75.665515032754797</v>
+      </c>
+      <c r="E29" s="2">
         <v>79.473300410063999</v>
       </c>
-      <c r="D29" s="2">
+      <c r="F29" s="2">
+        <v>77.156882653171806</v>
+      </c>
+      <c r="G29" s="2">
         <v>81.506477375301287</v>
       </c>
-      <c r="E29" s="2">
+      <c r="H29" s="2">
+        <v>96.545606982955604</v>
+      </c>
+      <c r="I29" s="2">
         <v>108.33307226743599</v>
       </c>
-      <c r="F29" s="2">
+      <c r="J29" s="2">
         <v>81.744073080033459</v>
       </c>
-    </row>
-    <row r="30" spans="1:6">
+      <c r="K29" s="2">
+        <v>83.611289598308687</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>43586</v>
       </c>
       <c r="B30" s="2">
+        <v>85.412396706132895</v>
+      </c>
+      <c r="C30" s="2">
         <v>89.786303180090002</v>
       </c>
-      <c r="C30" s="2">
+      <c r="D30" s="2">
+        <v>76.823817294287693</v>
+      </c>
+      <c r="E30" s="2">
         <v>77.506697847757096</v>
       </c>
-      <c r="D30" s="2">
+      <c r="F30" s="2">
+        <v>82.407734453491983</v>
+      </c>
+      <c r="G30" s="2">
         <v>82.892622096623995</v>
       </c>
-      <c r="E30" s="2">
+      <c r="H30" s="2">
+        <v>103.046554413583</v>
+      </c>
+      <c r="I30" s="2">
         <v>107.462730307515</v>
       </c>
-      <c r="F30" s="2">
+      <c r="J30" s="2">
         <v>84.836516992273815</v>
       </c>
-    </row>
-    <row r="31" spans="1:6">
+      <c r="K30" s="2">
+        <v>84.307872271682456</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>43617</v>
       </c>
       <c r="B31" s="2">
+        <v>92.561271711530893</v>
+      </c>
+      <c r="C31" s="2">
         <v>90.497008725079695</v>
       </c>
-      <c r="C31" s="2">
+      <c r="D31" s="2">
+        <v>81.80597343287269</v>
+      </c>
+      <c r="E31" s="2">
         <v>78.975400666783301</v>
       </c>
-      <c r="D31" s="2">
+      <c r="F31" s="2">
+        <v>87.276126167896891</v>
+      </c>
+      <c r="G31" s="2">
         <v>83.364976324882505</v>
       </c>
-      <c r="E31" s="2">
+      <c r="H31" s="2">
+        <v>101.544569117145</v>
+      </c>
+      <c r="I31" s="2">
         <v>104.053014960011</v>
       </c>
-      <c r="F31" s="2">
+      <c r="J31" s="2">
         <v>82.012312799338844</v>
       </c>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="K31" s="2">
+        <v>80.694772810448683</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>43647</v>
       </c>
       <c r="B32" s="2">
+        <v>92.828923816413692</v>
+      </c>
+      <c r="C32" s="2">
         <v>89.308076482690794</v>
       </c>
-      <c r="C32" s="2">
+      <c r="D32" s="2">
+        <v>80.21349544993339</v>
+      </c>
+      <c r="E32" s="2">
         <v>78.167797793017797</v>
       </c>
-      <c r="D32" s="2">
+      <c r="F32" s="2">
+        <v>85.426818520484701</v>
+      </c>
+      <c r="G32" s="2">
         <v>81.040270773091891</v>
       </c>
-      <c r="E32" s="2">
+      <c r="H32" s="2">
+        <v>101.549198854585</v>
+      </c>
+      <c r="I32" s="2">
         <v>101.480280170661</v>
       </c>
-      <c r="F32" s="2">
+      <c r="J32" s="2">
         <v>86.107260125184112</v>
       </c>
-    </row>
-    <row r="33" spans="1:6">
+      <c r="K32" s="2">
+        <v>84.434194381999234</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>43678</v>
       </c>
       <c r="B33" s="2">
+        <v>91.692911623643198</v>
+      </c>
+      <c r="C33" s="2">
         <v>88.21628249529509</v>
       </c>
-      <c r="C33" s="2">
+      <c r="D33" s="2">
+        <v>82.320728832138101</v>
+      </c>
+      <c r="E33" s="2">
         <v>80.666609179555394</v>
       </c>
-      <c r="D33" s="2">
+      <c r="F33" s="2">
+        <v>88.7322200526323</v>
+      </c>
+      <c r="G33" s="2">
         <v>83.061634836788187</v>
       </c>
-      <c r="E33" s="2">
+      <c r="H33" s="2">
+        <v>102.177207208309</v>
+      </c>
+      <c r="I33" s="2">
         <v>99.729937316905705</v>
       </c>
-      <c r="F33" s="2">
+      <c r="J33" s="2">
         <v>81.310831748758474</v>
       </c>
-    </row>
-    <row r="34" spans="1:6">
+      <c r="K33" s="2">
+        <v>82.080036678027398</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>43709</v>
       </c>
       <c r="B34" s="2">
+        <v>95.710913562767786</v>
+      </c>
+      <c r="C34" s="2">
         <v>89.721771255113097</v>
       </c>
-      <c r="C34" s="2">
+      <c r="D34" s="2">
+        <v>89.989024583955299</v>
+      </c>
+      <c r="E34" s="2">
         <v>85.424771775495401</v>
       </c>
-      <c r="D34" s="2">
+      <c r="F34" s="2">
+        <v>87.651091769308493</v>
+      </c>
+      <c r="G34" s="2">
         <v>83.97102870706729</v>
       </c>
-      <c r="E34" s="2">
+      <c r="H34" s="2">
+        <v>105.373061651737</v>
+      </c>
+      <c r="I34" s="2">
         <v>100.725151637712</v>
       </c>
-      <c r="F34" s="2">
+      <c r="J34" s="2">
         <v>88.332888845677459</v>
       </c>
-    </row>
-    <row r="35" spans="1:6">
+      <c r="K34" s="2">
+        <v>85.154340303889285</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>43739</v>
       </c>
       <c r="B35" s="2">
+        <v>93.723030718796394</v>
+      </c>
+      <c r="C35" s="2">
         <v>90.2138096206222</v>
       </c>
-      <c r="C35" s="2">
+      <c r="D35" s="2">
+        <v>87.38932743695409</v>
+      </c>
+      <c r="E35" s="2">
         <v>84.741250715004</v>
       </c>
-      <c r="D35" s="2">
+      <c r="F35" s="2">
+        <v>85.299141665509083</v>
+      </c>
+      <c r="G35" s="2">
         <v>84.681968097643392</v>
       </c>
-      <c r="E35" s="2">
+      <c r="H35" s="2">
+        <v>108.632766170883</v>
+      </c>
+      <c r="I35" s="2">
         <v>100.448351018412</v>
       </c>
-      <c r="F35" s="2">
+      <c r="J35" s="2">
         <v>88.336422145190141</v>
       </c>
-    </row>
-    <row r="36" spans="1:6">
+      <c r="K35" s="2">
+        <v>84.031351760777383</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>43770</v>
       </c>
       <c r="B36" s="2">
+        <v>88.871186761210694</v>
+      </c>
+      <c r="C36" s="2">
         <v>90.170394293681895</v>
       </c>
-      <c r="C36" s="2">
+      <c r="D36" s="2">
+        <v>86.444400022699909</v>
+      </c>
+      <c r="E36" s="2">
         <v>84.33161989640719</v>
       </c>
-      <c r="D36" s="2">
+      <c r="F36" s="2">
+        <v>85.550285102937394</v>
+      </c>
+      <c r="G36" s="2">
         <v>85.784922887273893</v>
       </c>
-      <c r="E36" s="2">
+      <c r="H36" s="2">
+        <v>116.072278067686</v>
+      </c>
+      <c r="I36" s="2">
         <v>103.605265315447</v>
       </c>
-      <c r="F36" s="2">
+      <c r="J36" s="2">
         <v>87.313783548102094</v>
       </c>
-    </row>
-    <row r="37" spans="1:6">
+      <c r="K36" s="2">
+        <v>84.568335041350608</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>43800</v>
       </c>
       <c r="B37" s="2">
+        <v>120.14930183597501</v>
+      </c>
+      <c r="C37" s="2">
         <v>94.240808170548902</v>
       </c>
-      <c r="C37" s="2">
+      <c r="D37" s="2">
+        <v>102.499065914238</v>
+      </c>
+      <c r="E37" s="2">
         <v>88.852601830336695</v>
       </c>
-      <c r="D37" s="2">
+      <c r="F37" s="2">
+        <v>101.433705762907</v>
+      </c>
+      <c r="G37" s="2">
         <v>88.345697628308599</v>
       </c>
-      <c r="E37" s="2">
+      <c r="H37" s="2">
+        <v>126.26144225740001</v>
+      </c>
+      <c r="I37" s="2">
         <v>104.94127718654801</v>
       </c>
-      <c r="F37" s="2">
+      <c r="J37" s="2">
         <v>94.65031416550103</v>
       </c>
-    </row>
-    <row r="38" spans="1:6">
+      <c r="K37" s="2">
+        <v>86.269997635569112</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>43831</v>
       </c>
       <c r="B38" s="2">
+        <v>76.899408050624189</v>
+      </c>
+      <c r="C38" s="2">
         <v>93.768968429424206</v>
       </c>
-      <c r="C38" s="2">
+      <c r="D38" s="2">
+        <v>74.421068257087597</v>
+      </c>
+      <c r="E38" s="2">
         <v>88.943563203447894</v>
       </c>
-      <c r="D38" s="2">
+      <c r="F38" s="2">
+        <v>74.754189269427584</v>
+      </c>
+      <c r="G38" s="2">
         <v>88.283102575254802</v>
       </c>
-      <c r="E38" s="2">
+      <c r="H38" s="2">
+        <v>102.783593411773</v>
+      </c>
+      <c r="I38" s="2">
         <v>102.398704466777</v>
       </c>
-      <c r="F38" s="2">
+      <c r="J38" s="2">
         <v>77.827132540180472</v>
       </c>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="K38" s="2">
+        <v>86.035778032663416</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>43862</v>
       </c>
       <c r="B39" s="2">
+        <v>78.019859158095599</v>
+      </c>
+      <c r="C39" s="2">
         <v>93.680048228345612</v>
       </c>
-      <c r="C39" s="2">
+      <c r="D39" s="2">
+        <v>76.1241792529582</v>
+      </c>
+      <c r="E39" s="2">
         <v>88.79246257025541</v>
       </c>
-      <c r="D39" s="2">
+      <c r="F39" s="2">
+        <v>75.956721384410102</v>
+      </c>
+      <c r="G39" s="2">
         <v>90.07607677003999</v>
       </c>
-      <c r="E39" s="2">
+      <c r="H39" s="2">
+        <v>91.393619352792001</v>
+      </c>
+      <c r="I39" s="2">
         <v>100.453537652073</v>
       </c>
-      <c r="F39" s="2">
+      <c r="J39" s="2">
         <v>78.991169786448438</v>
       </c>
-    </row>
-    <row r="40" spans="1:6">
+      <c r="K39" s="2">
+        <v>88.27499865794924</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>43891</v>
       </c>
       <c r="B40" s="2">
+        <v>77.642179886179406</v>
+      </c>
+      <c r="C40" s="2">
         <v>81.819699547186801</v>
       </c>
-      <c r="C40" s="2">
+      <c r="D40" s="2">
+        <v>83.451025667228194</v>
+      </c>
+      <c r="E40" s="2">
         <v>82.65300426092459</v>
       </c>
-      <c r="D40" s="2">
+      <c r="F40" s="2">
+        <v>81.382089589570995</v>
+      </c>
+      <c r="G40" s="2">
         <v>84.76251634607199</v>
       </c>
-      <c r="E40" s="2">
+      <c r="H40" s="2">
+        <v>77.904391506569297</v>
+      </c>
+      <c r="I40" s="2">
         <v>96.138026530005703</v>
       </c>
-      <c r="F40" s="2">
+      <c r="J40" s="2">
         <v>83.80134713950909</v>
       </c>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="K40" s="2">
+        <v>82.857377415615275</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>43922</v>
       </c>
       <c r="B41" s="2">
+        <v>57.080653966135195</v>
+      </c>
+      <c r="C41" s="2">
         <v>64.484863986168193</v>
       </c>
-      <c r="C41" s="2">
+      <c r="D41" s="2">
+        <v>58.543677846249295</v>
+      </c>
+      <c r="E41" s="2">
         <v>61.814042112534899</v>
       </c>
-      <c r="D41" s="2">
+      <c r="F41" s="2">
+        <v>64.106987073480312</v>
+      </c>
+      <c r="G41" s="2">
         <v>67.798267570094296</v>
       </c>
-      <c r="E41" s="2">
+      <c r="H41" s="2">
+        <v>77.705489511667807</v>
+      </c>
+      <c r="I41" s="2">
         <v>89.158073946515401</v>
       </c>
-      <c r="F41" s="2">
+      <c r="J41" s="2">
         <v>56.030803231773632</v>
       </c>
-    </row>
-    <row r="42" spans="1:6">
+      <c r="K41" s="2">
+        <v>58.567603553617886</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>43952</v>
       </c>
       <c r="B42" s="2">
+        <v>62.808263619018895</v>
+      </c>
+      <c r="C42" s="2">
         <v>69.354999095543789</v>
       </c>
-      <c r="C42" s="2">
+      <c r="D42" s="2">
+        <v>70.667380805343498</v>
+      </c>
+      <c r="E42" s="2">
         <v>72.40269251206621</v>
       </c>
-      <c r="D42" s="2">
+      <c r="F42" s="2">
+        <v>70.686928302598602</v>
+      </c>
+      <c r="G42" s="2">
         <v>73.081939298686592</v>
       </c>
-      <c r="E42" s="2">
+      <c r="H42" s="2">
+        <v>82.0417301348362</v>
+      </c>
+      <c r="I42" s="2">
         <v>86.945042999085203</v>
       </c>
-      <c r="F42" s="2">
+      <c r="J42" s="2">
         <v>69.509011476969434</v>
       </c>
-    </row>
-    <row r="43" spans="1:6">
+      <c r="K42" s="2">
+        <v>69.496938980835594</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>43983</v>
       </c>
       <c r="B43" s="2">
+        <v>75.755070019793507</v>
+      </c>
+      <c r="C43" s="2">
         <v>74.396370204032081</v>
       </c>
-      <c r="C43" s="2">
+      <c r="D43" s="2">
+        <v>89.587913752208195</v>
+      </c>
+      <c r="E43" s="2">
         <v>85.956713027534093</v>
       </c>
-      <c r="D43" s="2">
+      <c r="F43" s="2">
+        <v>88.886229498223102</v>
+      </c>
+      <c r="G43" s="2">
         <v>84.690386437628689</v>
       </c>
-      <c r="E43" s="2">
+      <c r="H43" s="2">
+        <v>86.275472524191002</v>
+      </c>
+      <c r="I43" s="2">
         <v>89.383543130867096</v>
       </c>
-      <c r="F43" s="2">
+      <c r="J43" s="2">
         <v>81.677620721657135</v>
       </c>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="K43" s="2">
+        <v>80.421134089605118</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>44013</v>
       </c>
       <c r="B44" s="2">
+        <v>83.142547229181289</v>
+      </c>
+      <c r="C44" s="2">
         <v>79.906050154156588</v>
       </c>
-      <c r="C44" s="2">
+      <c r="D44" s="2">
+        <v>98.065190279492711</v>
+      </c>
+      <c r="E44" s="2">
         <v>94.315006652155901</v>
       </c>
-      <c r="D44" s="2">
+      <c r="F44" s="2">
+        <v>97.555364332209095</v>
+      </c>
+      <c r="G44" s="2">
         <v>91.001542982278096</v>
       </c>
-      <c r="E44" s="2">
+      <c r="H44" s="2">
+        <v>99.658669209890505</v>
+      </c>
+      <c r="I44" s="2">
         <v>99.877955909695302</v>
       </c>
-      <c r="F44" s="2">
+      <c r="J44" s="2">
         <v>90.31153143065751</v>
       </c>
-    </row>
-    <row r="45" spans="1:6">
+      <c r="K44" s="2">
+        <v>89.233303027573101</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>44044</v>
       </c>
       <c r="B45" s="2">
+        <v>86.679602363274697</v>
+      </c>
+      <c r="C45" s="2">
         <v>82.738899149615293</v>
       </c>
-      <c r="C45" s="2">
+      <c r="D45" s="2">
+        <v>94.061648165426192</v>
+      </c>
+      <c r="E45" s="2">
         <v>92.383467252509689</v>
       </c>
-      <c r="D45" s="2">
+      <c r="F45" s="2">
+        <v>95.301597193646799</v>
+      </c>
+      <c r="G45" s="2">
         <v>89.644112718942296</v>
       </c>
-      <c r="E45" s="2">
+      <c r="H45" s="2">
+        <v>110.16225296838</v>
+      </c>
+      <c r="I45" s="2">
         <v>107.46547216778799</v>
       </c>
-      <c r="F45" s="2">
+      <c r="J45" s="2">
         <v>89.518057235315268</v>
       </c>
-    </row>
-    <row r="46" spans="1:6">
+      <c r="K45" s="2">
+        <v>90.586947799216375</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>44075</v>
       </c>
       <c r="B46" s="2">
+        <v>91.219110138755809</v>
+      </c>
+      <c r="C46" s="2">
         <v>83.536897227356505</v>
       </c>
-      <c r="C46" s="2">
+      <c r="D46" s="2">
+        <v>100.22602010251499</v>
+      </c>
+      <c r="E46" s="2">
         <v>94.606922950919198</v>
       </c>
-      <c r="D46" s="2">
+      <c r="F46" s="2">
+        <v>97.083928120925805</v>
+      </c>
+      <c r="G46" s="2">
         <v>91.786774191057603</v>
       </c>
-      <c r="E46" s="2">
+      <c r="H46" s="2">
+        <v>111.07327103583501</v>
+      </c>
+      <c r="I46" s="2">
         <v>106.34809453002499</v>
       </c>
-      <c r="F46" s="2">
+      <c r="J46" s="2">
         <v>95.419061003305146</v>
       </c>
-    </row>
-    <row r="47" spans="1:6">
+      <c r="K46" s="2">
+        <v>92.534226000565027</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>44105</v>
       </c>
       <c r="B47" s="2">
+        <v>91.042693032597597</v>
+      </c>
+      <c r="C47" s="2">
         <v>85.83573893660909</v>
       </c>
-      <c r="C47" s="2">
+      <c r="D47" s="2">
+        <v>98.418103527074692</v>
+      </c>
+      <c r="E47" s="2">
         <v>94.139154118276778</v>
       </c>
-      <c r="D47" s="2">
+      <c r="F47" s="2">
+        <v>97.272699114058398</v>
+      </c>
+      <c r="G47" s="2">
         <v>94.7882105732875</v>
       </c>
-      <c r="E47" s="2">
+      <c r="H47" s="2">
+        <v>114.41186109858</v>
+      </c>
+      <c r="I47" s="2">
         <v>105.792013611226</v>
       </c>
-      <c r="F47" s="2">
+      <c r="J47" s="2">
         <v>97.536541901473996</v>
       </c>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="K47" s="2">
+        <v>92.680823126780112</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>44136</v>
       </c>
       <c r="B48" s="2">
+        <v>89.581392901962587</v>
+      </c>
+      <c r="C48" s="2">
         <v>89.110273619497093</v>
       </c>
-      <c r="C48" s="2">
+      <c r="D48" s="2">
+        <v>102.08852955326101</v>
+      </c>
+      <c r="E48" s="2">
         <v>98.673421214363188</v>
       </c>
-      <c r="D48" s="2">
+      <c r="F48" s="2">
+        <v>96.779800655504999</v>
+      </c>
+      <c r="G48" s="2">
         <v>95.336134785230612</v>
       </c>
-      <c r="E48" s="2">
+      <c r="H48" s="2">
+        <v>118.54866017270901</v>
+      </c>
+      <c r="I48" s="2">
         <v>105.84328918678101</v>
       </c>
-      <c r="F48" s="2">
+      <c r="J48" s="2">
         <v>97.185833346083001</v>
       </c>
-    </row>
-    <row r="49" spans="1:6">
+      <c r="K48" s="2">
+        <v>93.886235976938011</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>44166</v>
       </c>
       <c r="B49" s="2">
+        <v>118.181342408604</v>
+      </c>
+      <c r="C49" s="2">
         <v>89.737900993144109</v>
       </c>
-      <c r="C49" s="2">
+      <c r="D49" s="2">
+        <v>108.64656560997901</v>
+      </c>
+      <c r="E49" s="2">
         <v>94.614834980970713</v>
       </c>
-      <c r="D49" s="2">
+      <c r="F49" s="2">
+        <v>104.12037532253099</v>
+      </c>
+      <c r="G49" s="2">
         <v>91.002260992052399</v>
       </c>
-      <c r="E49" s="2">
+      <c r="H49" s="2">
+        <v>127.482295386784</v>
+      </c>
+      <c r="I49" s="2">
         <v>106.081701230001</v>
       </c>
-      <c r="F49" s="2">
+      <c r="J49" s="2">
         <v>103.12112690101434</v>
       </c>
-    </row>
-    <row r="50" spans="1:6">
+      <c r="K49" s="2">
+        <v>94.363519467303476</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>44197</v>
       </c>
       <c r="B50" s="2">
+        <v>71.064790650754105</v>
+      </c>
+      <c r="C50" s="2">
         <v>90.161196519989787</v>
       </c>
-      <c r="C50" s="2">
+      <c r="D50" s="2">
+        <v>81.211245148465679</v>
+      </c>
+      <c r="E50" s="2">
         <v>97.756083783761483</v>
       </c>
-      <c r="D50" s="2">
+      <c r="F50" s="2">
+        <v>77.313107525939998</v>
+      </c>
+      <c r="G50" s="2">
         <v>94.096760918568393</v>
       </c>
-      <c r="E50" s="2">
+      <c r="H50" s="2">
+        <v>99.530099468406206</v>
+      </c>
+      <c r="I50" s="2">
         <v>99.247202215101396</v>
       </c>
-      <c r="F50" s="2">
+      <c r="J50" s="2">
         <v>87.510323013913364</v>
       </c>
-    </row>
-    <row r="51" spans="1:6">
+      <c r="K50" s="2">
+        <v>96.317239242468531</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>44228</v>
       </c>
       <c r="B51" s="2">
+        <v>74.01781919145391</v>
+      </c>
+      <c r="C51" s="2">
         <v>92.457292986790904</v>
       </c>
-      <c r="C51" s="2">
+      <c r="D51" s="2">
+        <v>84.706874403948703</v>
+      </c>
+      <c r="E51" s="2">
         <v>99.614636553338187</v>
       </c>
-      <c r="D51" s="2">
+      <c r="F51" s="2">
+        <v>79.863172025612997</v>
+      </c>
+      <c r="G51" s="2">
         <v>96.989422750440298</v>
       </c>
-      <c r="E51" s="2">
+      <c r="H51" s="2">
+        <v>91.184127578988395</v>
+      </c>
+      <c r="I51" s="2">
         <v>100.08579463581501</v>
       </c>
-      <c r="F51" s="2">
+      <c r="J51" s="2">
         <v>86.205811838649964</v>
       </c>
-    </row>
-    <row r="52" spans="1:6">
+      <c r="K51" s="2">
+        <v>96.566457629988662</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>44256</v>
       </c>
       <c r="B52" s="2">
+        <v>89.0345010666028</v>
+      </c>
+      <c r="C52" s="2">
         <v>95.222021957085005</v>
       </c>
-      <c r="C52" s="2">
+      <c r="D52" s="2">
+        <v>101.447071875153</v>
+      </c>
+      <c r="E52" s="2">
         <v>100.732083712952</v>
       </c>
-      <c r="D52" s="2">
+      <c r="F52" s="2">
+        <v>95.980960110994999</v>
+      </c>
+      <c r="G52" s="2">
         <v>101.034771574148</v>
       </c>
-      <c r="E52" s="2">
+      <c r="H52" s="2">
+        <v>80.353158399532902</v>
+      </c>
+      <c r="I52" s="2">
         <v>98.359005723999104</v>
       </c>
-      <c r="F52" s="2">
+      <c r="J52" s="2">
         <v>97.969814394133948</v>
       </c>
-    </row>
-    <row r="53" spans="1:6">
+      <c r="K52" s="2">
+        <v>96.667867268585212</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>44287</v>
       </c>
       <c r="B53" s="2">
+        <v>82.865009078571205</v>
+      </c>
+      <c r="C53" s="2">
         <v>93.581099467427308</v>
       </c>
-      <c r="C53" s="2">
+      <c r="D53" s="2">
+        <v>88.857364362593188</v>
+      </c>
+      <c r="E53" s="2">
         <v>93.632279733776798</v>
       </c>
-      <c r="D53" s="2">
+      <c r="F53" s="2">
+        <v>88.548836814989187</v>
+      </c>
+      <c r="G53" s="2">
         <v>93.353171436022578</v>
       </c>
-      <c r="E53" s="2">
+      <c r="H53" s="2">
+        <v>87.0261490547189</v>
+      </c>
+      <c r="I53" s="2">
         <v>98.113963635155002</v>
       </c>
-      <c r="F53" s="2">
+      <c r="J53" s="2">
         <v>93.451911001220012</v>
       </c>
-    </row>
-    <row r="54" spans="1:6">
+      <c r="K53" s="2">
+        <v>96.774853915888627</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>44317</v>
       </c>
       <c r="B54" s="2">
+        <v>83.875576765832108</v>
+      </c>
+      <c r="C54" s="2">
         <v>92.729584382833508</v>
       </c>
-      <c r="C54" s="2">
+      <c r="D54" s="2">
+        <v>92.97816610843131</v>
+      </c>
+      <c r="E54" s="2">
         <v>94.829699848211391</v>
       </c>
-      <c r="D54" s="2">
+      <c r="F54" s="2">
+        <v>88.4703685255419</v>
+      </c>
+      <c r="G54" s="2">
         <v>91.981746458984304</v>
       </c>
-      <c r="E54" s="2">
+      <c r="H54" s="2">
+        <v>92.356680851122405</v>
+      </c>
+      <c r="I54" s="2">
         <v>96.834447906792704</v>
       </c>
-      <c r="F54" s="2">
+      <c r="J54" s="2">
         <v>99.155661759559862</v>
       </c>
-    </row>
-    <row r="55" spans="1:6">
+      <c r="K54" s="2">
+        <v>98.815389087610029</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>44348</v>
       </c>
       <c r="B55" s="2">
+        <v>98.961915544302883</v>
+      </c>
+      <c r="C55" s="2">
         <v>97.246015292971805</v>
       </c>
-      <c r="C55" s="2">
+      <c r="D55" s="2">
+        <v>105.012642091602</v>
+      </c>
+      <c r="E55" s="2">
         <v>100.58479815053799</v>
       </c>
-      <c r="D55" s="2">
+      <c r="F55" s="2">
+        <v>103.76266820611001</v>
+      </c>
+      <c r="G55" s="2">
         <v>98.301283180264306</v>
       </c>
-      <c r="E55" s="2">
+      <c r="H55" s="2">
+        <v>92.460222266622495</v>
+      </c>
+      <c r="I55" s="2">
         <v>95.164619869389895</v>
       </c>
-      <c r="F55" s="2">
+      <c r="J55" s="2">
         <v>101.22004873573334</v>
       </c>
-    </row>
-    <row r="56" spans="1:6">
+      <c r="K55" s="2">
+        <v>99.94506500951222</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>44378</v>
       </c>
       <c r="B56" s="2">
+        <v>108.629446553449</v>
+      </c>
+      <c r="C56" s="2">
         <v>102.503943097172</v>
       </c>
-      <c r="C56" s="2">
+      <c r="D56" s="2">
+        <v>100.48461382227801</v>
+      </c>
+      <c r="E56" s="2">
         <v>97.8900795627262</v>
       </c>
-      <c r="D56" s="2">
+      <c r="F56" s="2">
+        <v>110.647735759833</v>
+      </c>
+      <c r="G56" s="2">
         <v>102.48054139113201</v>
       </c>
-      <c r="E56" s="2">
+      <c r="H56" s="2">
+        <v>97.628147454243106</v>
+      </c>
+      <c r="I56" s="2">
         <v>98.181290162993804</v>
       </c>
-      <c r="F56" s="2">
+      <c r="J56" s="2">
         <v>99.173976895296576</v>
       </c>
-    </row>
-    <row r="57" spans="1:6">
+      <c r="K56" s="2">
+        <v>98.078929863722053</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>44409</v>
       </c>
       <c r="B57" s="2">
+        <v>109.97354316823899</v>
+      </c>
+      <c r="C57" s="2">
         <v>102.200555720933</v>
       </c>
-      <c r="C57" s="2">
+      <c r="D57" s="2">
+        <v>101.41426909635101</v>
+      </c>
+      <c r="E57" s="2">
         <v>100.647494474249</v>
       </c>
-      <c r="D57" s="2">
+      <c r="F57" s="2">
+        <v>108.345596249243</v>
+      </c>
+      <c r="G57" s="2">
         <v>102.03586743228301</v>
       </c>
-      <c r="E57" s="2">
+      <c r="H57" s="2">
+        <v>102.30984686503101</v>
+      </c>
+      <c r="I57" s="2">
         <v>100.506084009681</v>
       </c>
-      <c r="F57" s="2">
+      <c r="J57" s="2">
         <v>101.2325412758739</v>
       </c>
-    </row>
-    <row r="58" spans="1:6">
+      <c r="K57" s="2">
+        <v>103.00162985207234</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>44440</v>
       </c>
       <c r="B58" s="2">
+        <v>116.242546856182</v>
+      </c>
+      <c r="C58" s="2">
         <v>106.08177645811301</v>
       </c>
-      <c r="C58" s="2">
+      <c r="D58" s="2">
+        <v>106.39727094084</v>
+      </c>
+      <c r="E58" s="2">
         <v>101.281001146004</v>
       </c>
-      <c r="D58" s="2">
+      <c r="F58" s="2">
+        <v>110.56806190372301</v>
+      </c>
+      <c r="G58" s="2">
         <v>103.53474952426799</v>
       </c>
-      <c r="E58" s="2">
+      <c r="H58" s="2">
+        <v>107.11040636031299</v>
+      </c>
+      <c r="I58" s="2">
         <v>103.384733194676</v>
       </c>
-      <c r="F58" s="2">
+      <c r="J58" s="2">
         <v>103.68018653522523</v>
       </c>
-    </row>
-    <row r="59" spans="1:6">
+      <c r="K58" s="2">
+        <v>101.25480641100224</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>44470</v>
       </c>
       <c r="B59" s="2">
+        <v>112.51666736604201</v>
+      </c>
+      <c r="C59" s="2">
         <v>106.205778993446</v>
       </c>
-      <c r="C59" s="2">
+      <c r="D59" s="2">
+        <v>107.113618146947</v>
+      </c>
+      <c r="E59" s="2">
         <v>103.06166633503099</v>
       </c>
-      <c r="D59" s="2">
+      <c r="F59" s="2">
+        <v>108.82738925998201</v>
+      </c>
+      <c r="G59" s="2">
         <v>105.137216898296</v>
       </c>
-      <c r="E59" s="2">
+      <c r="H59" s="2">
+        <v>113.934276132151</v>
+      </c>
+      <c r="I59" s="2">
         <v>105.97991036364</v>
       </c>
-      <c r="F59" s="2">
+      <c r="J59" s="2">
         <v>105.97374728676499</v>
       </c>
-    </row>
-    <row r="60" spans="1:6">
+      <c r="K59" s="2">
+        <v>102.14430079012439</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>44501</v>
       </c>
       <c r="B60" s="2">
+        <v>111.41466614943</v>
+      </c>
+      <c r="C60" s="2">
         <v>111.27599371318</v>
       </c>
-      <c r="C60" s="2">
+      <c r="D60" s="2">
+        <v>112.29473981848</v>
+      </c>
+      <c r="E60" s="2">
         <v>107.98763368906999</v>
       </c>
-      <c r="D60" s="2">
+      <c r="F60" s="2">
+        <v>109.60314517242202</v>
+      </c>
+      <c r="G60" s="2">
         <v>106.987248485225</v>
       </c>
-      <c r="E60" s="2">
+      <c r="H60" s="2">
+        <v>116.224880747084</v>
+      </c>
+      <c r="I60" s="2">
         <v>104.41461549350799</v>
       </c>
-      <c r="F60" s="2">
+      <c r="J60" s="2">
         <v>107.81017119727846</v>
       </c>
-    </row>
-    <row r="61" spans="1:6">
+      <c r="K60" s="2">
+        <v>105.23793744524413</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>44531</v>
       </c>
       <c r="B61" s="2">
+        <v>141.40351760914101</v>
+      </c>
+      <c r="C61" s="2">
         <v>110.334741410058</v>
       </c>
-      <c r="C61" s="2">
+      <c r="D61" s="2">
+        <v>118.08212418491001</v>
+      </c>
+      <c r="E61" s="2">
         <v>101.982543010342</v>
       </c>
-      <c r="D61" s="2">
+      <c r="F61" s="2">
+        <v>118.06895844560799</v>
+      </c>
+      <c r="G61" s="2">
         <v>104.067219950368</v>
       </c>
-      <c r="E61" s="2">
+      <c r="H61" s="2">
+        <v>119.88200482178701</v>
+      </c>
+      <c r="I61" s="2">
         <v>99.728332789249606</v>
       </c>
-      <c r="F61" s="2">
+      <c r="J61" s="2">
         <v>116.61580606635007</v>
       </c>
-    </row>
-    <row r="62" spans="1:6">
+      <c r="K61" s="2">
+        <v>105.19552348378122</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>44562</v>
       </c>
       <c r="B62" s="2">
+        <v>89.475214674821501</v>
+      </c>
+      <c r="C62" s="2">
         <v>110.05046802832301</v>
       </c>
-      <c r="C62" s="2">
-        <v>96.236194314374401</v>
-      </c>
       <c r="D62" s="2">
-        <v>102.018016272162</v>
+        <v>80.377931216392682</v>
       </c>
       <c r="E62" s="2">
+        <v>96.194803457322692</v>
+      </c>
+      <c r="F62" s="2">
+        <v>84.949732171761198</v>
+      </c>
+      <c r="G62" s="2">
+        <v>102.00681316512399</v>
+      </c>
+      <c r="H62" s="2">
+        <v>93.134473128412793</v>
+      </c>
+      <c r="I62" s="2">
         <v>93.081612187991198</v>
       </c>
-      <c r="F62" s="2">
-        <v>92.760893587794769</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
+      <c r="J62" s="2">
+        <v>92.762235592382723</v>
+      </c>
+      <c r="K62" s="2">
+        <v>102.16139587525588</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>44593</v>
       </c>
       <c r="B63" s="2">
+        <v>91.246016126363287</v>
+      </c>
+      <c r="C63" s="2">
         <v>111.462492416589</v>
       </c>
-      <c r="C63" s="2">
-        <v>100.864084203979</v>
-      </c>
       <c r="D63" s="2">
-        <v>104.704086680633</v>
+        <v>86.137186114169708</v>
       </c>
       <c r="E63" s="2">
+        <v>100.85347690593301</v>
+      </c>
+      <c r="F63" s="2">
+        <v>86.100671828650292</v>
+      </c>
+      <c r="G63" s="2">
+        <v>104.70678195842001</v>
+      </c>
+      <c r="H63" s="2">
+        <v>83.187470237914397</v>
+      </c>
+      <c r="I63" s="2">
         <v>92.362034316566294</v>
       </c>
-      <c r="F63" s="2">
-        <v>96.818885390411921</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
+      <c r="J63" s="2">
+        <v>96.820729784815029</v>
+      </c>
+      <c r="K63" s="2">
+        <v>108.24340255306811</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>44621</v>
       </c>
       <c r="B64" s="2">
+        <v>110.34705289436</v>
+      </c>
+      <c r="C64" s="2">
         <v>116.12529196832899</v>
       </c>
-      <c r="C64" s="2">
-        <v>101.120323704387</v>
-      </c>
       <c r="D64" s="2">
-        <v>104.201742697491</v>
+        <v>103.701789810986</v>
       </c>
       <c r="E64" s="2">
+        <v>101.12156091876501</v>
+      </c>
+      <c r="F64" s="2">
+        <v>100.91185160178399</v>
+      </c>
+      <c r="G64" s="2">
+        <v>104.16634024957901</v>
+      </c>
+      <c r="H64" s="2">
+        <v>75.778788906588403</v>
+      </c>
+      <c r="I64" s="2">
         <v>93.404241507893701</v>
       </c>
-      <c r="F64" s="2">
-        <v>105.85083230057451</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
+      <c r="J64" s="2">
+        <v>105.85597917372932</v>
+      </c>
+      <c r="K64" s="2">
+        <v>103.83452028014136</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>44652</v>
       </c>
       <c r="B65" s="2">
+        <v>107.786202314874</v>
+      </c>
+      <c r="C65" s="2">
         <v>117.93833788402601</v>
       </c>
-      <c r="C65" s="2">
-        <v>105.43102354999002</v>
-      </c>
       <c r="D65" s="2">
-        <v>107.177958912818</v>
+        <v>101.28603953545399</v>
       </c>
       <c r="E65" s="2">
+        <v>105.43740068984401</v>
+      </c>
+      <c r="F65" s="2">
+        <v>102.471977357222</v>
+      </c>
+      <c r="G65" s="2">
+        <v>107.18671068680399</v>
+      </c>
+      <c r="H65" s="2">
+        <v>87.013739071118394</v>
+      </c>
+      <c r="I65" s="2">
         <v>97.555573896023304</v>
       </c>
-      <c r="F65" s="2">
-        <v>102.26932041962284</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
+      <c r="J65" s="2">
+        <v>102.27370556387064</v>
+      </c>
+      <c r="K65" s="2">
+        <v>106.38815545330037</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>44682</v>
       </c>
       <c r="B66" s="2">
+        <v>116.198029528665</v>
+      </c>
+      <c r="C66" s="2">
         <v>121.14226326150501</v>
       </c>
-      <c r="C66" s="2">
-        <v>105.513660007685</v>
-      </c>
       <c r="D66" s="2">
-        <v>110.68093545228301</v>
+        <v>104.990671842338</v>
       </c>
       <c r="E66" s="2">
+        <v>105.49620704132501</v>
+      </c>
+      <c r="F66" s="2">
+        <v>108.244941216697</v>
+      </c>
+      <c r="G66" s="2">
+        <v>110.68000728868</v>
+      </c>
+      <c r="H66" s="2">
+        <v>93.077819843238004</v>
+      </c>
+      <c r="I66" s="2">
         <v>97.141534639937703</v>
       </c>
-      <c r="F66" s="2">
-        <v>105.94448636380483</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
+      <c r="J66" s="2">
+        <v>105.93786555294426</v>
+      </c>
+      <c r="K66" s="2">
+        <v>105.68882340359572</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>44713</v>
       </c>
       <c r="B67" s="2">
+        <v>128.79753645189402</v>
+      </c>
+      <c r="C67" s="2">
         <v>124.506502385179</v>
       </c>
-      <c r="C67" s="2">
-        <v>103.269900985099</v>
-      </c>
       <c r="D67" s="2">
-        <v>107.12519448601401</v>
+        <v>108.81114443935301</v>
       </c>
       <c r="E67" s="2">
+        <v>103.25927760658901</v>
+      </c>
+      <c r="F67" s="2">
+        <v>112.25592014310401</v>
+      </c>
+      <c r="G67" s="2">
+        <v>107.15327960899801</v>
+      </c>
+      <c r="H67" s="2">
+        <v>94.012043290121696</v>
+      </c>
+      <c r="I67" s="2">
         <v>96.452521679938599</v>
       </c>
-      <c r="F67" s="2">
-        <v>109.38601857526596</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
+      <c r="J67" s="2">
+        <v>109.39095569097864</v>
+      </c>
+      <c r="K67" s="2">
+        <v>107.74510070870112</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>44743</v>
       </c>
       <c r="B68" s="2">
+        <v>124.47476865196201</v>
+      </c>
+      <c r="C68" s="2">
         <v>120.25451198560501</v>
       </c>
-      <c r="C68" s="2">
-        <v>101.593479696342</v>
-      </c>
       <c r="D68" s="2">
-        <v>109.82007597031901</v>
+        <v>101.95551660972001</v>
       </c>
       <c r="E68" s="2">
+        <v>101.60911887917199</v>
+      </c>
+      <c r="F68" s="2">
+        <v>116.16455182403399</v>
+      </c>
+      <c r="G68" s="2">
+        <v>109.85913813391201</v>
+      </c>
+      <c r="H68" s="2">
+        <v>90.691835923632297</v>
+      </c>
+      <c r="I68" s="2">
         <v>92.446928039346304</v>
       </c>
-      <c r="F68" s="2">
-        <v>100.98243172057923</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
+      <c r="J68" s="2">
+        <v>100.96914745760942</v>
+      </c>
+      <c r="K68" s="2">
+        <v>100.05407777408563</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>44774</v>
       </c>
       <c r="B69" s="2">
+        <v>127.12985707230401</v>
+      </c>
+      <c r="C69" s="2">
         <v>122.10488771581501</v>
       </c>
-      <c r="C69" s="2">
-        <v>108.20433252758301</v>
-      </c>
       <c r="D69" s="2">
-        <v>117.01353222096601</v>
+        <v>107.043228489201</v>
       </c>
       <c r="E69" s="2">
+        <v>108.19944949692801</v>
+      </c>
+      <c r="F69" s="2">
+        <v>121.88899219615401</v>
+      </c>
+      <c r="G69" s="2">
+        <v>117.049321224987</v>
+      </c>
+      <c r="H69" s="2">
+        <v>93.811337322225398</v>
+      </c>
+      <c r="I69" s="2">
         <v>93.9159165666414</v>
       </c>
-      <c r="F69" s="2">
-        <v>102.11191355199917</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
+      <c r="J69" s="2">
+        <v>102.11605572535009</v>
+      </c>
+      <c r="K69" s="2">
+        <v>103.87163411504925</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>44805</v>
       </c>
       <c r="B70" s="2">
+        <v>131.51944429419601</v>
+      </c>
+      <c r="C70" s="2">
         <v>123.402027501969</v>
       </c>
-      <c r="C70" s="2">
-        <v>110.85559713019001</v>
-      </c>
       <c r="D70" s="2">
-        <v>119.158890371361</v>
+        <v>115.09957759893</v>
       </c>
       <c r="E70" s="2">
+        <v>110.852936155268</v>
+      </c>
+      <c r="F70" s="2">
+        <v>125.06870539804501</v>
+      </c>
+      <c r="G70" s="2">
+        <v>119.19451358382301</v>
+      </c>
+      <c r="H70" s="2">
+        <v>91.219670425178506</v>
+      </c>
+      <c r="I70" s="2">
         <v>89.740361584064999</v>
       </c>
-      <c r="F70" s="2">
-        <v>103.7306013367408</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
+      <c r="J70" s="2">
+        <v>103.73603547173332</v>
+      </c>
+      <c r="K70" s="2">
+        <v>101.35214795672408</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>44835</v>
       </c>
       <c r="B71" s="2">
+        <v>127.96787162920701</v>
+      </c>
+      <c r="C71" s="2">
         <v>123.13356929134501</v>
       </c>
-      <c r="C71" s="2">
-        <v>113.34259893175799</v>
-      </c>
       <c r="D71" s="2">
-        <v>122.338367191331</v>
+        <v>115.11108649374201</v>
       </c>
       <c r="E71" s="2">
+        <v>113.33551667615801</v>
+      </c>
+      <c r="F71" s="2">
+        <v>124.53831791033301</v>
+      </c>
+      <c r="G71" s="2">
+        <v>122.35622667227101</v>
+      </c>
+      <c r="H71" s="2">
+        <v>100.590313662304</v>
+      </c>
+      <c r="I71" s="2">
         <v>93.392550871839802</v>
       </c>
-      <c r="F71" s="2">
-        <v>108.47525795209313</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
+      <c r="J71" s="2">
+        <v>108.47699166545972</v>
+      </c>
+      <c r="K71" s="2">
+        <v>104.87914449412889</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>44866</v>
       </c>
       <c r="B72" s="2">
+        <v>123.519484068891</v>
+      </c>
+      <c r="C72" s="2">
         <v>123.94995633630801</v>
       </c>
-      <c r="C72" s="2">
-        <v>112.008164200138</v>
-      </c>
       <c r="D72" s="2">
-        <v>124.547021045242</v>
+        <v>114.23694736978901</v>
       </c>
       <c r="E72" s="2">
+        <v>112.073736346221</v>
+      </c>
+      <c r="F72" s="2">
+        <v>125.45569916643299</v>
+      </c>
+      <c r="G72" s="2">
+        <v>124.404704205017</v>
+      </c>
+      <c r="H72" s="2">
+        <v>103.68730151701899</v>
+      </c>
+      <c r="I72" s="2">
         <v>93.308772934683603</v>
       </c>
-      <c r="F72" s="2">
-        <v>105.94191104770202</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
+      <c r="J72" s="2">
+        <v>105.94620778857598</v>
+      </c>
+      <c r="K72" s="2">
+        <v>103.62885482186522</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>44896</v>
       </c>
       <c r="B73" s="2">
+        <v>163.730394440856</v>
+      </c>
+      <c r="C73" s="2">
         <v>127.340420246333</v>
       </c>
-      <c r="C73" s="2">
-        <v>117.04028164658</v>
-      </c>
       <c r="D73" s="2">
-        <v>128.39374793860298</v>
+        <v>138.39156250303202</v>
       </c>
       <c r="E73" s="2">
+        <v>117.074342725058</v>
+      </c>
+      <c r="F73" s="2">
+        <v>146.94586633935901</v>
+      </c>
+      <c r="G73" s="2">
+        <v>128.29874071637499</v>
+      </c>
+      <c r="H73" s="2">
+        <v>114.32008499606999</v>
+      </c>
+      <c r="I73" s="2">
         <v>93.624203006266399</v>
       </c>
-      <c r="F73" s="2">
-        <v>118.62961055461983</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
+      <c r="J73" s="2">
+        <v>118.63306920526081</v>
+      </c>
+      <c r="K73" s="2">
+        <v>104.91246962107979</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>44927</v>
       </c>
       <c r="B74" s="2">
+        <v>103.968139507789</v>
+      </c>
+      <c r="C74" s="2">
         <v>125.986908577704</v>
       </c>
-      <c r="C74" s="2">
-        <v>125.54605958917401</v>
-      </c>
       <c r="D74" s="2">
-        <v>133.37151633079299</v>
+        <v>106.21908620326401</v>
       </c>
       <c r="E74" s="2">
+        <v>125.480224383063</v>
+      </c>
+      <c r="F74" s="2">
+        <v>114.15628119835101</v>
+      </c>
+      <c r="G74" s="2">
+        <v>133.38176394890701</v>
+      </c>
+      <c r="H74" s="2">
+        <v>96.827568367797994</v>
+      </c>
+      <c r="I74" s="2">
         <v>93.578776829672293</v>
       </c>
-      <c r="F74" s="2">
-        <v>96.448559899016928</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
+      <c r="J74" s="2">
+        <v>96.453006327033179</v>
+      </c>
+      <c r="K74" s="2">
+        <v>106.19262819517652</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>44958</v>
       </c>
       <c r="B75" s="2">
+        <v>95.616573070564712</v>
+      </c>
+      <c r="C75" s="2">
         <v>118.35428247499</v>
       </c>
-      <c r="C75" s="2">
-        <v>115.36035061436901</v>
-      </c>
       <c r="D75" s="2">
-        <v>126.50729066955302</v>
+        <v>98.948058446294795</v>
       </c>
       <c r="E75" s="2">
+        <v>115.34173544310801</v>
+      </c>
+      <c r="F75" s="2">
+        <v>105.408040910208</v>
+      </c>
+      <c r="G75" s="2">
+        <v>126.529617265591</v>
+      </c>
+      <c r="H75" s="2">
+        <v>87.402467483863504</v>
+      </c>
+      <c r="I75" s="2">
         <v>93.126272572027403</v>
       </c>
-      <c r="F75" s="2">
-        <v>88.337815768566301</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
+      <c r="J75" s="2">
+        <v>88.339576465005649</v>
+      </c>
+      <c r="K75" s="2">
+        <v>99.386699814668248</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>44986</v>
       </c>
       <c r="B76" s="2">
+        <v>115.71899044305199</v>
+      </c>
+      <c r="C76" s="2">
         <v>123.795934705192</v>
       </c>
-      <c r="C76" s="2">
-        <v>118.144869363539</v>
-      </c>
       <c r="D76" s="2">
-        <v>134.01561809785201</v>
+        <v>121.52480833416999</v>
       </c>
       <c r="E76" s="2">
+        <v>118.135013869525</v>
+      </c>
+      <c r="F76" s="2">
+        <v>130.44997949184202</v>
+      </c>
+      <c r="G76" s="2">
+        <v>134.04330036879603</v>
+      </c>
+      <c r="H76" s="2">
+        <v>83.5117312023377</v>
+      </c>
+      <c r="I76" s="2">
         <v>98.215718944919601</v>
       </c>
-      <c r="F76" s="2">
-        <v>106.25135930747567</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
+      <c r="J76" s="2">
+        <v>106.2582702218596</v>
+      </c>
+      <c r="K76" s="2">
+        <v>104.93643041852899</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>45017</v>
       </c>
       <c r="B77" s="2">
+        <v>116.02964291613399</v>
+      </c>
+      <c r="C77" s="2">
         <v>126.97306459780201</v>
       </c>
-      <c r="C77" s="2">
-        <v>120.917974697277</v>
-      </c>
       <c r="D77" s="2">
-        <v>139.20759674064402</v>
+        <v>117.59716782715201</v>
       </c>
       <c r="E77" s="2">
+        <v>120.92985448646</v>
+      </c>
+      <c r="F77" s="2">
+        <v>133.942148824046</v>
+      </c>
+      <c r="G77" s="2">
+        <v>139.24913433771599</v>
+      </c>
+      <c r="H77" s="2">
+        <v>89.938939382036395</v>
+      </c>
+      <c r="I77" s="2">
         <v>99.285925609550901</v>
       </c>
-      <c r="F77" s="2">
-        <v>100.81614195885119</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
+      <c r="J77" s="2">
+        <v>100.80983394675752</v>
+      </c>
+      <c r="K77" s="2">
+        <v>105.75644149853451</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>45047</v>
       </c>
       <c r="B78" s="2">
+        <v>125.931278910578</v>
+      </c>
+      <c r="C78" s="2">
         <v>130.471336285192</v>
       </c>
-      <c r="C78" s="2">
-        <v>124.251341333185</v>
-      </c>
       <c r="D78" s="2">
-        <v>142.41642636303501</v>
+        <v>124.648252542628</v>
       </c>
       <c r="E78" s="2">
+        <v>124.227289680645</v>
+      </c>
+      <c r="F78" s="2">
+        <v>141.356537219388</v>
+      </c>
+      <c r="G78" s="2">
+        <v>142.41485877586902</v>
+      </c>
+      <c r="H78" s="2">
+        <v>98.087821268120805</v>
+      </c>
+      <c r="I78" s="2">
         <v>101.83976433213699</v>
       </c>
-      <c r="F78" s="2">
-        <v>106.26560669416172</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
+      <c r="J78" s="2">
+        <v>106.26919966680163</v>
+      </c>
+      <c r="K78" s="2">
+        <v>106.67753330734104</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>45078</v>
       </c>
       <c r="B79" s="2">
+        <v>132.00010396274399</v>
+      </c>
+      <c r="C79" s="2">
         <v>127.03953738464901</v>
       </c>
-      <c r="C79" s="2">
-        <v>121.91823525053299</v>
-      </c>
       <c r="D79" s="2">
-        <v>141.37851912589599</v>
+        <v>128.786401806535</v>
       </c>
       <c r="E79" s="2">
+        <v>121.91409843830499</v>
+      </c>
+      <c r="F79" s="2">
+        <v>146.916144813876</v>
+      </c>
+      <c r="G79" s="2">
+        <v>141.38699885193299</v>
+      </c>
+      <c r="H79" s="2">
+        <v>100.744011243222</v>
+      </c>
+      <c r="I79" s="2">
         <v>103.52413376198</v>
       </c>
-      <c r="F79" s="2">
-        <v>110.27487854972547</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
+      <c r="J79" s="2">
+        <v>110.2629671005471</v>
+      </c>
+      <c r="K79" s="2">
+        <v>109.17061700123666</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>45108</v>
       </c>
       <c r="B80" s="2">
+        <v>134.83609990925601</v>
+      </c>
+      <c r="C80" s="2">
         <v>128.44438144956899</v>
       </c>
-      <c r="C80" s="2">
-        <v>127.73623374445602</v>
-      </c>
       <c r="D80" s="2">
-        <v>147.04421730096203</v>
+        <v>128.17227017461201</v>
       </c>
       <c r="E80" s="2">
+        <v>127.76582138171501</v>
+      </c>
+      <c r="F80" s="2">
+        <v>153.867257396626</v>
+      </c>
+      <c r="G80" s="2">
+        <v>147.113115150075</v>
+      </c>
+      <c r="H80" s="2">
+        <v>99.096989263855903</v>
+      </c>
+      <c r="I80" s="2">
         <v>101.61378815516299</v>
       </c>
-      <c r="F80" s="2">
-        <v>109.37942546815148</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
+      <c r="J80" s="2">
+        <v>109.37991422846075</v>
+      </c>
+      <c r="K80" s="2">
+        <v>108.63326825936218</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>45139</v>
       </c>
       <c r="B81" s="2">
+        <v>133.82591575631403</v>
+      </c>
+      <c r="C81" s="2">
         <v>128.09833049459999</v>
       </c>
-      <c r="C81" s="2">
-        <v>122.0127183319</v>
-      </c>
       <c r="D81" s="2">
-        <v>140.38390340643602</v>
+        <v>120.24585482263601</v>
       </c>
       <c r="E81" s="2">
+        <v>122.031524947929</v>
+      </c>
+      <c r="F81" s="2">
+        <v>144.630335441287</v>
+      </c>
+      <c r="G81" s="2">
+        <v>140.491359573886</v>
+      </c>
+      <c r="H81" s="2">
+        <v>98.878999064498203</v>
+      </c>
+      <c r="I81" s="2">
         <v>101.33614013650499</v>
       </c>
-      <c r="F81" s="2">
-        <v>105.74397622924614</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
+      <c r="J81" s="2">
+        <v>105.74856445515492</v>
+      </c>
+      <c r="K81" s="2">
+        <v>107.89029464163133</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>45170</v>
       </c>
       <c r="B82" s="2">
+        <v>136.51135263516301</v>
+      </c>
+      <c r="C82" s="2">
         <v>127.96438328568101</v>
       </c>
-      <c r="C82" s="2">
-        <v>117.76336894435001</v>
-      </c>
       <c r="D82" s="2">
-        <v>140.38717541419101</v>
+        <v>121.454694867424</v>
       </c>
       <c r="E82" s="2">
+        <v>117.76792731601901</v>
+      </c>
+      <c r="F82" s="2">
+        <v>145.04783042989101</v>
+      </c>
+      <c r="G82" s="2">
+        <v>140.41090932770601</v>
+      </c>
+      <c r="H82" s="2">
+        <v>102.86290605196599</v>
+      </c>
+      <c r="I82" s="2">
         <v>102.535167669305</v>
       </c>
-      <c r="F82" s="2">
-        <v>109.09936121372981</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
+      <c r="J82" s="2">
+        <v>109.10141649884692</v>
+      </c>
+      <c r="K82" s="2">
+        <v>107.62203371411499</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>45200</v>
       </c>
       <c r="B83" s="2">
+        <v>136.053082579581</v>
+      </c>
+      <c r="C83" s="2">
         <v>130.48146195307299</v>
       </c>
-      <c r="C83" s="2">
-        <v>123.14083924679501</v>
-      </c>
       <c r="D83" s="2">
-        <v>143.312856850022</v>
+        <v>123.56931240589401</v>
       </c>
       <c r="E83" s="2">
+        <v>123.144216386549</v>
+      </c>
+      <c r="F83" s="2">
+        <v>143.83702366879601</v>
+      </c>
+      <c r="G83" s="2">
+        <v>143.278994080519</v>
+      </c>
+      <c r="H83" s="2">
+        <v>109.900718988915</v>
+      </c>
+      <c r="I83" s="2">
         <v>104.989190112816</v>
       </c>
-      <c r="F83" s="2">
-        <v>111.30173141675765</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
+      <c r="J83" s="2">
+        <v>111.30853478832037</v>
+      </c>
+      <c r="K83" s="2">
+        <v>107.03318065769277</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>45231</v>
       </c>
       <c r="B84" s="2">
+        <v>125.688434548331</v>
+      </c>
+      <c r="C84" s="2">
         <v>128.22253405170099</v>
       </c>
-      <c r="C84" s="2">
-        <v>122.726687753072</v>
-      </c>
       <c r="D84" s="2">
-        <v>144.81696835820901</v>
+        <v>124.056663662303</v>
       </c>
       <c r="E84" s="2">
+        <v>122.81615151002801</v>
+      </c>
+      <c r="F84" s="2">
+        <v>144.92371386168398</v>
+      </c>
+      <c r="G84" s="2">
+        <v>144.55844216675101</v>
+      </c>
+      <c r="H84" s="2">
+        <v>112.70541817653</v>
+      </c>
+      <c r="I84" s="2">
         <v>104.960014003251</v>
       </c>
-      <c r="F84" s="2">
-        <v>108.03285317487638</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
+      <c r="J84" s="2">
+        <v>108.03781326990082</v>
+      </c>
+      <c r="K84" s="2">
+        <v>105.05448634151857</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>45261</v>
       </c>
       <c r="B85" s="2">
+        <v>164.70777702663901</v>
+      </c>
+      <c r="C85" s="2">
         <v>129.85205944313401</v>
       </c>
-      <c r="C85" s="2">
-        <v>127.52603293283001</v>
-      </c>
       <c r="D85" s="2">
-        <v>148.17767053016902</v>
+        <v>151.54140033159001</v>
       </c>
       <c r="E85" s="2">
+        <v>127.51129335406701</v>
+      </c>
+      <c r="F85" s="2">
+        <v>169.423326988962</v>
+      </c>
+      <c r="G85" s="2">
+        <v>147.85343466964798</v>
+      </c>
+      <c r="H85" s="2">
+        <v>126.20025442717601</v>
+      </c>
+      <c r="I85" s="2">
         <v>106.646590352332</v>
       </c>
-      <c r="F85" s="2">
-        <v>121.39291778931316</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
+      <c r="J85" s="2">
+        <v>121.39335148376523</v>
+      </c>
+      <c r="K85" s="2">
+        <v>107.30958724238378</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>45292</v>
       </c>
       <c r="B86" s="2">
+        <v>105.890296412645</v>
+      </c>
+      <c r="C86" s="2">
         <v>128.86194457624902</v>
       </c>
-      <c r="C86" s="2">
-        <v>126.03173387344999</v>
-      </c>
       <c r="D86" s="2">
-        <v>151.34171160871298</v>
+        <v>107.85949624126401</v>
       </c>
       <c r="E86" s="2">
+        <v>126.621205458025</v>
+      </c>
+      <c r="F86" s="2">
+        <v>129.819663580297</v>
+      </c>
+      <c r="G86" s="2">
+        <v>150.83871011339201</v>
+      </c>
+      <c r="H86" s="2">
+        <v>117.929327210883</v>
+      </c>
+      <c r="I86" s="2">
         <v>112.086941911087</v>
       </c>
-      <c r="F86" s="2">
-        <v>97.696167379532469</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
+      <c r="J86" s="2">
+        <v>97.70077727866861</v>
+      </c>
+      <c r="K86" s="2">
+        <v>107.72119686762525</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>45323</v>
       </c>
       <c r="B87" s="2">
+        <v>109.720811566915</v>
+      </c>
+      <c r="C87" s="2">
         <v>132.32632428071301</v>
       </c>
-      <c r="C87" s="2">
-        <v>128.67073719620501</v>
-      </c>
       <c r="D87" s="2">
-        <v>155.68582079556001</v>
+        <v>112.411897555702</v>
       </c>
       <c r="E87" s="2">
+        <v>129.388187326815</v>
+      </c>
+      <c r="F87" s="2">
+        <v>132.83626067078603</v>
+      </c>
+      <c r="G87" s="2">
+        <v>155.23914296466401</v>
+      </c>
+      <c r="H87" s="2">
+        <v>112.920675946296</v>
+      </c>
+      <c r="I87" s="2">
         <v>115.70982726392801</v>
       </c>
-      <c r="F87" s="2">
-        <v>98.209900166303598</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
+      <c r="J87" s="2">
+        <v>98.220230906339808</v>
+      </c>
+      <c r="K87" s="2">
+        <v>110.93720792574157</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>45352</v>
       </c>
       <c r="B88" s="2">
+        <v>124.311268943804</v>
+      </c>
+      <c r="C88" s="2">
         <v>132.44542248896499</v>
       </c>
-      <c r="C88" s="2">
-        <v>130.67305261757599</v>
-      </c>
       <c r="D88" s="2">
-        <v>156.82617314351498</v>
+        <v>136.699855153827</v>
       </c>
       <c r="E88" s="2">
+        <v>131.43205873201501</v>
+      </c>
+      <c r="F88" s="2">
+        <v>156.27858681034101</v>
+      </c>
+      <c r="G88" s="2">
+        <v>156.248798084599</v>
+      </c>
+      <c r="H88" s="2">
+        <v>102.289483128079</v>
+      </c>
+      <c r="I88" s="2">
         <v>115.617834756364</v>
       </c>
-      <c r="F88" s="2">
-        <v>110.85402508600323</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
+      <c r="J88" s="2">
+        <v>110.85214680263283</v>
+      </c>
+      <c r="K88" s="2">
+        <v>109.34975545154479</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>45383</v>
       </c>
       <c r="B89" s="2">
+        <v>119.40777958290001</v>
+      </c>
+      <c r="C89" s="2">
         <v>129.36377167664298</v>
       </c>
-      <c r="C89" s="2">
-        <v>126.86148630008201</v>
-      </c>
       <c r="D89" s="2">
-        <v>154.37318407664398</v>
+        <v>122.26470205594001</v>
       </c>
       <c r="E89" s="2">
+        <v>127.586128187809</v>
+      </c>
+      <c r="F89" s="2">
+        <v>148.06733538470601</v>
+      </c>
+      <c r="G89" s="2">
+        <v>153.80813011288299</v>
+      </c>
+      <c r="H89" s="2">
+        <v>106.007029143905</v>
+      </c>
+      <c r="I89" s="2">
         <v>115.607364804078</v>
       </c>
-      <c r="F89" s="2">
-        <v>99.761332151851491</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
+      <c r="J89" s="2">
+        <v>99.751743948754424</v>
+      </c>
+      <c r="K89" s="2">
+        <v>104.73726308764545</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>45413</v>
       </c>
       <c r="B90" s="2">
+        <v>127.86532142001501</v>
+      </c>
+      <c r="C90" s="2">
         <v>130.88135057558401</v>
       </c>
-      <c r="C90" s="2">
-        <v>122.360780731375</v>
-      </c>
       <c r="D90" s="2">
-        <v>152.818667119856</v>
+        <v>121.94962599406901</v>
       </c>
       <c r="E90" s="2">
+        <v>123.09218534575101</v>
+      </c>
+      <c r="F90" s="2">
+        <v>150.903387158632</v>
+      </c>
+      <c r="G90" s="2">
+        <v>152.40659681596298</v>
+      </c>
+      <c r="H90" s="2">
+        <v>107.277499069436</v>
+      </c>
+      <c r="I90" s="2">
         <v>111.499425167528</v>
       </c>
-      <c r="F90" s="2">
-        <v>106.32285683766368</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
+      <c r="J90" s="2">
+        <v>106.32983651674299</v>
+      </c>
+      <c r="K90" s="2">
+        <v>106.45286261705425</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>45444</v>
       </c>
       <c r="B91" s="2">
+        <v>134.74810341919598</v>
+      </c>
+      <c r="C91" s="2">
         <v>129.55579435683399</v>
       </c>
-      <c r="C91" s="2">
-        <v>122.960349125058</v>
-      </c>
       <c r="D91" s="2">
-        <v>155.96269637297502</v>
+        <v>129.453910530592</v>
       </c>
       <c r="E91" s="2">
+        <v>123.809461255044</v>
+      </c>
+      <c r="F91" s="2">
+        <v>160.194466117367</v>
+      </c>
+      <c r="G91" s="2">
+        <v>155.60260199673598</v>
+      </c>
+      <c r="H91" s="2">
+        <v>108.254409445595</v>
+      </c>
+      <c r="I91" s="2">
         <v>111.461061960566</v>
       </c>
-      <c r="F91" s="2">
-        <v>104.8054800053262</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
+      <c r="J91" s="2">
+        <v>104.79126130031895</v>
+      </c>
+      <c r="K91" s="2">
+        <v>104.08860555373299</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>45474</v>
       </c>
       <c r="B92" s="2">
+        <v>134.68999785252399</v>
+      </c>
+      <c r="C92" s="2">
         <v>129.53403644708902</v>
       </c>
-      <c r="C92" s="2">
-        <v>125.39805750652201</v>
-      </c>
       <c r="D92" s="2">
-        <v>158.32507781617801</v>
+        <v>125.50641998464499</v>
       </c>
       <c r="E92" s="2">
+        <v>126.25475678043</v>
+      </c>
+      <c r="F92" s="2">
+        <v>162.761661055703</v>
+      </c>
+      <c r="G92" s="2">
+        <v>157.97370727248702</v>
+      </c>
+      <c r="H92" s="2">
+        <v>111.932436656669</v>
+      </c>
+      <c r="I92" s="2">
         <v>113.939787748366</v>
       </c>
-      <c r="F92" s="2">
-        <v>105.20133378484498</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
+      <c r="J92" s="2">
+        <v>105.2057786418156</v>
+      </c>
+      <c r="K92" s="2">
+        <v>104.86741607241896</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>45505</v>
       </c>
       <c r="B93" s="2">
+        <v>133.753080919675</v>
+      </c>
+      <c r="C93" s="2">
         <v>129.220913073785</v>
       </c>
-      <c r="C93" s="2">
-        <v>129.516339435075</v>
-      </c>
       <c r="D93" s="2">
-        <v>160.96325326681</v>
+        <v>128.454290156448</v>
       </c>
       <c r="E93" s="2">
+        <v>130.51675047523503</v>
+      </c>
+      <c r="F93" s="2">
+        <v>164.01093355978603</v>
+      </c>
+      <c r="G93" s="2">
+        <v>160.55633053979503</v>
+      </c>
+      <c r="H93" s="2">
+        <v>110.514179242156</v>
+      </c>
+      <c r="I93" s="2">
         <v>113.56146383758499</v>
       </c>
-      <c r="F93" s="2">
-        <v>100.39321875117218</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
+      <c r="J93" s="2">
+        <v>100.39509256108353</v>
+      </c>
+      <c r="K93" s="2">
+        <v>103.26725051907697</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>45536</v>
       </c>
       <c r="B94" s="2">
+        <v>137.303940847565</v>
+      </c>
+      <c r="C94" s="2">
         <v>130.30437220738301</v>
       </c>
-      <c r="C94" s="2">
-        <v>132.56597096861901</v>
-      </c>
       <c r="D94" s="2">
-        <v>164.35352162297798</v>
+        <v>138.49798112419901</v>
       </c>
       <c r="E94" s="2">
+        <v>133.56206661165302</v>
+      </c>
+      <c r="F94" s="2">
+        <v>169.15715119207701</v>
+      </c>
+      <c r="G94" s="2">
+        <v>164.12452678370002</v>
+      </c>
+      <c r="H94" s="2">
+        <v>115.171242644486</v>
+      </c>
+      <c r="I94" s="2">
         <v>114.226311548479</v>
       </c>
-      <c r="F94" s="2">
-        <v>106.68751340408902</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
+      <c r="J94" s="2">
+        <v>106.68890682900933</v>
+      </c>
+      <c r="K94" s="2">
+        <v>104.91866698176017</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>45566</v>
       </c>
       <c r="B95" s="2">
+        <v>134.66323007315103</v>
+      </c>
+      <c r="C95" s="2">
         <v>130.46389205792002</v>
       </c>
-      <c r="C95" s="2">
-        <v>131.89571550189402</v>
-      </c>
       <c r="D95" s="2">
-        <v>164.801376788499</v>
+        <v>133.91358084279798</v>
       </c>
       <c r="E95" s="2">
+        <v>132.95722757203001</v>
+      </c>
+      <c r="F95" s="2">
+        <v>165.43254587244502</v>
+      </c>
+      <c r="G95" s="2">
+        <v>164.57122310525401</v>
+      </c>
+      <c r="H95" s="2">
+        <v>117.80667270798899</v>
+      </c>
+      <c r="I95" s="2">
         <v>114.15574820860699</v>
       </c>
-      <c r="F95" s="2">
-        <v>108.0412799125279</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
+      <c r="J95" s="2">
+        <v>108.04512132759515</v>
+      </c>
+      <c r="K95" s="2">
+        <v>104.17386141489024</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>45597</v>
       </c>
       <c r="B96" s="2">
+        <v>126.84577603666601</v>
+      </c>
+      <c r="C96" s="2">
         <v>130.63763244261202</v>
       </c>
-      <c r="C96" s="2">
-        <v>132.878200195066</v>
-      </c>
       <c r="D96" s="2">
-        <v>167.31092974716901</v>
+        <v>136.21834705970699</v>
       </c>
       <c r="E96" s="2">
+        <v>134.12632510009001</v>
+      </c>
+      <c r="F96" s="2">
+        <v>168.29410706528401</v>
+      </c>
+      <c r="G96" s="2">
+        <v>167.266102978894</v>
+      </c>
+      <c r="H96" s="2">
+        <v>125.5150622343</v>
+      </c>
+      <c r="I96" s="2">
         <v>118.573393637998</v>
       </c>
-      <c r="F96" s="2">
-        <v>109.86738089849621</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
+      <c r="J96" s="2">
+        <v>109.86931993809515</v>
+      </c>
+      <c r="K96" s="2">
+        <v>107.04520764975092</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>45627</v>
       </c>
       <c r="B97" s="2">
+        <v>168.30123278737699</v>
+      </c>
+      <c r="C97" s="2">
         <v>131.704875995349</v>
       </c>
-      <c r="C97" s="2">
-        <v>139.26244957066302</v>
-      </c>
       <c r="D97" s="2">
-        <v>168.41471164588</v>
+        <v>167.90169928784098</v>
       </c>
       <c r="E97" s="2">
+        <v>140.73582037162902</v>
+      </c>
+      <c r="F97" s="2">
+        <v>193.901970206675</v>
+      </c>
+      <c r="G97" s="2">
+        <v>168.431766703797</v>
+      </c>
+      <c r="H97" s="2">
+        <v>144.34804046385301</v>
+      </c>
+      <c r="I97" s="2">
         <v>124.182566361818</v>
       </c>
-      <c r="F97" s="2">
-        <v>129.88624010287273</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
+      <c r="J97" s="2">
+        <v>129.89032659393405</v>
+      </c>
+      <c r="K97" s="2">
+        <v>112.61675095579356</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>45658</v>
       </c>
       <c r="B98" s="2">
+        <v>113.406047482006</v>
+      </c>
+      <c r="C98" s="2">
         <v>136.24539514084202</v>
       </c>
-      <c r="C98" s="2">
-        <v>134.25613573334499</v>
-      </c>
       <c r="D98" s="2">
-        <v>171.418980303778</v>
+        <v>114.283178369897</v>
       </c>
       <c r="E98" s="2">
+        <v>135.261271135805</v>
+      </c>
+      <c r="F98" s="2">
+        <v>146.80852993105501</v>
+      </c>
+      <c r="G98" s="2">
+        <v>171.73847563399499</v>
+      </c>
+      <c r="H98" s="2">
+        <v>136.94830507389099</v>
+      </c>
+      <c r="I98" s="2">
         <v>129.295073839856</v>
       </c>
-      <c r="F98" s="2">
-        <v>98.866813654143456</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
+      <c r="J98" s="2">
+        <v>98.728392293962258</v>
+      </c>
+      <c r="K98" s="2">
+        <v>109.37384910862868</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>45689</v>
       </c>
       <c r="B99" s="2">
+        <v>111.116828811269</v>
+      </c>
+      <c r="C99" s="2">
         <v>133.83765126476902</v>
       </c>
-      <c r="C99" s="2">
-        <v>137.79577647129702</v>
-      </c>
       <c r="D99" s="2">
-        <v>173.16487681455502</v>
+        <v>120.071339414668</v>
       </c>
       <c r="E99" s="2">
+        <v>138.62595831388199</v>
+      </c>
+      <c r="F99" s="2">
+        <v>149.37127139120901</v>
+      </c>
+      <c r="G99" s="2">
+        <v>173.25889756852999</v>
+      </c>
+      <c r="H99" s="2">
+        <v>127.36822414250901</v>
+      </c>
+      <c r="I99" s="2">
         <v>129.784878933871</v>
       </c>
-      <c r="F99" s="2">
-        <v>96.326798724346702</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
+      <c r="J99" s="2">
+        <v>96.245255244640049</v>
+      </c>
+      <c r="K99" s="2">
+        <v>107.56470022147617</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>45717</v>
       </c>
       <c r="B100" s="2">
+        <v>125.899200220102</v>
+      </c>
+      <c r="C100" s="2">
         <v>134.80008390310502</v>
       </c>
-      <c r="C100" s="2">
-        <v>144.428634034449</v>
-      </c>
       <c r="D100" s="2">
-        <v>170.94671648173602</v>
+        <v>152.29948420935003</v>
       </c>
       <c r="E100" s="2">
+        <v>145.16501010279401</v>
+      </c>
+      <c r="F100" s="2">
+        <v>172.45549871013901</v>
+      </c>
+      <c r="G100" s="2">
+        <v>171.28095581529001</v>
+      </c>
+      <c r="H100" s="2">
+        <v>113.960137172759</v>
+      </c>
+      <c r="I100" s="2">
         <v>128.84662877503601</v>
       </c>
-      <c r="F100" s="2">
-        <v>113.63882447962992</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
+      <c r="J100" s="2">
+        <v>113.43483154125632</v>
+      </c>
+      <c r="K100" s="2">
+        <v>111.17895661300406</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>45748</v>
       </c>
       <c r="B101" s="2">
+        <v>124.65355400154901</v>
+      </c>
+      <c r="C101" s="2">
         <v>133.92495010003802</v>
       </c>
-      <c r="C101" s="2">
-        <v>140.53557013509803</v>
-      </c>
       <c r="D101" s="2">
-        <v>175.39806064283701</v>
+        <v>135.175893337882</v>
       </c>
       <c r="E101" s="2">
+        <v>141.238931379485</v>
+      </c>
+      <c r="F101" s="2">
+        <v>166.433022567519</v>
+      </c>
+      <c r="G101" s="2">
+        <v>175.88230935767402</v>
+      </c>
+      <c r="H101" s="2">
+        <v>116.281986735332</v>
+      </c>
+      <c r="I101" s="2">
         <v>128.46635082331599</v>
       </c>
-      <c r="F101" s="2">
-        <v>102.94472164695473</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
+      <c r="J101" s="2">
+        <v>102.71967789713233</v>
+      </c>
+      <c r="K101" s="2">
+        <v>107.44556572763751</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>45778</v>
       </c>
       <c r="B102" s="2">
+        <v>133.281797154911</v>
+      </c>
+      <c r="C102" s="2">
         <v>135.72483520381402</v>
       </c>
-      <c r="C102" s="2">
-        <v>145.25157052489598</v>
-      </c>
       <c r="D102" s="2">
-        <v>178.55086009111901</v>
+        <v>145.63613044208901</v>
       </c>
       <c r="E102" s="2">
+        <v>145.88769983225103</v>
+      </c>
+      <c r="F102" s="2">
+        <v>178.51420699609201</v>
+      </c>
+      <c r="G102" s="2">
+        <v>179.070487542221</v>
+      </c>
+      <c r="H102" s="2">
+        <v>129.19420438362499</v>
+      </c>
+      <c r="I102" s="2">
         <v>134.39555596869599</v>
       </c>
-      <c r="F102" s="2">
-        <v>111.6249594566315</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
+      <c r="J102" s="2">
+        <v>111.42126584733693</v>
+      </c>
+      <c r="K102" s="2">
+        <v>110.91485019553939</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>45809</v>
       </c>
       <c r="B103" s="2">
+        <v>140.22962886082502</v>
+      </c>
+      <c r="C103" s="2">
         <v>135.22235343858802</v>
       </c>
-      <c r="C103" s="2">
-        <v>150.583549885927</v>
-      </c>
       <c r="D103" s="2">
-        <v>181.10630999443501</v>
+        <v>158.97038427330301</v>
       </c>
       <c r="E103" s="2">
+        <v>151.186940099125</v>
+      </c>
+      <c r="F103" s="2">
+        <v>185.25387041756102</v>
+      </c>
+      <c r="G103" s="2">
+        <v>181.47942702973199</v>
+      </c>
+      <c r="H103" s="2">
+        <v>134.752886573669</v>
+      </c>
+      <c r="I103" s="2">
         <v>137.85109381413699</v>
       </c>
-      <c r="F103" s="2">
-        <v>113.65665360991301</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
+      <c r="J103" s="2">
+        <v>113.36841173304488</v>
+      </c>
+      <c r="K103" s="2">
+        <v>111.61183774646872</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>45839</v>
       </c>
       <c r="B104" s="2">
+        <v>138.292197631091</v>
+      </c>
+      <c r="C104" s="2">
         <v>134.70068419255699</v>
       </c>
-      <c r="C104" s="2">
-        <v>141.329727964146</v>
-      </c>
       <c r="D104" s="2">
-        <v>181.11521289507101</v>
+        <v>140.516284654233</v>
       </c>
       <c r="E104" s="2">
+        <v>141.71707849240502</v>
+      </c>
+      <c r="F104" s="2">
+        <v>185.59296294431201</v>
+      </c>
+      <c r="G104" s="2">
+        <v>181.40577560780301</v>
+      </c>
+      <c r="H104" s="2">
+        <v>139.141774976341</v>
+      </c>
+      <c r="I104" s="2">
         <v>140.35033884370699</v>
       </c>
-      <c r="F104" s="2">
-        <v>110.64600280789678</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
+      <c r="J104" s="2">
+        <v>110.35347651454606</v>
+      </c>
+      <c r="K104" s="2">
+        <v>109.66680107798976</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>45870</v>
       </c>
       <c r="B105" s="2">
+        <v>139.192980645587</v>
+      </c>
+      <c r="C105" s="2">
         <v>135.52029088962601</v>
       </c>
-      <c r="C105" s="2">
-        <v>140.10200350333599</v>
-      </c>
       <c r="D105" s="2">
-        <v>183.33427682860702</v>
+        <v>138.11273429715203</v>
       </c>
       <c r="E105" s="2">
+        <v>140.43575768792999</v>
+      </c>
+      <c r="F105" s="2">
+        <v>186.746220683594</v>
+      </c>
+      <c r="G105" s="2">
+        <v>183.80472795778701</v>
+      </c>
+      <c r="H105" s="2">
+        <v>138.22167483439199</v>
+      </c>
+      <c r="I105" s="2">
         <v>140.830996378522</v>
       </c>
-      <c r="F105" s="2">
-        <v>107.75962736111829</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
+      <c r="J105" s="2">
+        <v>107.52457402598037</v>
+      </c>
+      <c r="K105" s="2">
+        <v>110.23026148881031</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>45901</v>
       </c>
       <c r="B106" s="2">
+        <v>142.153161076733</v>
+      </c>
+      <c r="C106" s="2">
         <v>135.44909239901</v>
       </c>
-      <c r="C106" s="2">
-        <v>147.081097625859</v>
-      </c>
       <c r="D106" s="2">
-        <v>187.72790231977001</v>
+        <v>153.256558541223</v>
       </c>
       <c r="E106" s="2">
+        <v>147.321657009917</v>
+      </c>
+      <c r="F106" s="2">
+        <v>195.15962288239402</v>
+      </c>
+      <c r="G106" s="2">
+        <v>188.05735777109899</v>
+      </c>
+      <c r="H106" s="2">
+        <v>149.48891021916199</v>
+      </c>
+      <c r="I106" s="2">
         <v>146.34053660664301</v>
       </c>
-      <c r="F106" s="2">
-        <v>109.84733499889029</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
+      <c r="J106" s="2">
+        <v>109.90844001063732</v>
+      </c>
+      <c r="K106" s="2">
+        <v>108.11251841982566</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>45931</v>
       </c>
       <c r="B107" s="2">
+        <v>139.51719748288099</v>
+      </c>
+      <c r="C107" s="2">
         <v>135.067198978768</v>
       </c>
-      <c r="C107" s="2">
-        <v>141.9</v>
-      </c>
       <c r="D107" s="2">
-        <v>188.05971905443903</v>
+        <v>143.286739613734</v>
       </c>
       <c r="E107" s="2">
+        <v>141.99431583561</v>
+      </c>
+      <c r="F107" s="2">
+        <v>191.13110405924499</v>
+      </c>
+      <c r="G107" s="2">
+        <v>188.53940670073501</v>
+      </c>
+      <c r="H107" s="2">
+        <v>151.18633642844699</v>
+      </c>
+      <c r="I107" s="2">
         <v>146.01616690997599</v>
       </c>
-      <c r="F107" s="2">
-        <v>110.45400035531898</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
+      <c r="J107" s="2">
+        <v>110.29292487896778</v>
+      </c>
+      <c r="K107" s="2">
+        <v>107.14967353478146</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>45962</v>
       </c>
       <c r="B108" s="2">
+        <v>131.93795505321302</v>
+      </c>
+      <c r="C108" s="2">
         <v>135.28444639522101</v>
       </c>
-      <c r="C108" s="2">
-        <v>142.69999999999999</v>
-      </c>
       <c r="D108" s="2">
-        <v>190.81</v>
+        <v>145.47110738957102</v>
       </c>
       <c r="E108" s="2">
+        <v>143.06505318470599</v>
+      </c>
+      <c r="F108" s="2">
+        <v>193.30050436650899</v>
+      </c>
+      <c r="G108" s="2">
+        <v>191.71150390691699</v>
+      </c>
+      <c r="H108" s="2">
+        <v>153.52063456070101</v>
+      </c>
+      <c r="I108" s="2">
         <v>145.8729283401</v>
       </c>
-      <c r="F108" s="2">
-        <v>112.47441128400352</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
-      <c r="F112" t="s">
-        <v>5</v>
+      <c r="J108" s="2">
+        <v>112.31400958934741</v>
+      </c>
+      <c r="K108" s="2">
+        <v>109.87524004997631</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A109" s="1">
+        <v>45992</v>
+      </c>
+      <c r="B109" s="2"/>
+      <c r="C109" s="2"/>
+      <c r="D109" s="2">
+        <v>174.29508107688102</v>
+      </c>
+      <c r="E109" s="2">
+        <v>146.13168696973202</v>
+      </c>
+      <c r="F109" s="2">
+        <v>225.58202442790503</v>
+      </c>
+      <c r="G109" s="2">
+        <v>194.96042674553701</v>
+      </c>
+      <c r="H109" s="2"/>
+      <c r="I109" s="2"/>
+      <c r="J109" s="2">
+        <v>127.18913761286116</v>
+      </c>
+      <c r="K109" s="2">
+        <v>111.2255593522179</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J112" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{9e923255-b694-4734-b055-efbd556a65fc}" enabled="1" method="Standard" siteId="{a71b8764-0a7a-4511-8f04-04867f0718ab}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>